--- a/database/event/6862/event_6862_evp_summary.xlsx
+++ b/database/event/6862/event_6862_evp_summary.xlsx
@@ -499,7 +499,7 @@
         <v>10.0996</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>8.1439</v>
       </c>
       <c r="D2" t="n">
         <v>3.6587</v>
@@ -545,7 +545,7 @@
         <v>9.895799999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>7.9796</v>
       </c>
       <c r="D3" t="n">
         <v>3.5763</v>
@@ -591,7 +591,7 @@
         <v>9.3003</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>7.4994</v>
       </c>
       <c r="D4" t="n">
         <v>3.3358</v>
@@ -637,7 +637,7 @@
         <v>8.700799999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>7.016</v>
       </c>
       <c r="D5" t="n">
         <v>3.0936</v>
@@ -683,7 +683,7 @@
         <v>8.279999999999999</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>6.6767</v>
       </c>
       <c r="D6" t="n">
         <v>2.9236</v>
@@ -729,7 +729,7 @@
         <v>6.6107</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>5.3306</v>
       </c>
       <c r="D7" t="n">
         <v>2.2492</v>
@@ -775,7 +775,7 @@
         <v>6.343</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>5.1147</v>
       </c>
       <c r="D8" t="n">
         <v>2.1411</v>
@@ -821,7 +821,7 @@
         <v>6.2315</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>5.0248</v>
       </c>
       <c r="D9" t="n">
         <v>2.096</v>
@@ -867,7 +867,7 @@
         <v>5.7488</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>4.6356</v>
       </c>
       <c r="D10" t="n">
         <v>1.901</v>
@@ -913,7 +913,7 @@
         <v>5.6587</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>4.5629</v>
       </c>
       <c r="D11" t="n">
         <v>1.8646</v>
@@ -959,7 +959,7 @@
         <v>5.6555</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>4.5604</v>
       </c>
       <c r="D12" t="n">
         <v>1.8633</v>
@@ -1005,7 +1005,7 @@
         <v>5.5666</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>4.4887</v>
       </c>
       <c r="D13" t="n">
         <v>1.8274</v>
@@ -1051,7 +1051,7 @@
         <v>5.4865</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>4.4241</v>
       </c>
       <c r="D14" t="n">
         <v>1.7951</v>
@@ -1097,7 +1097,7 @@
         <v>5.3506</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>4.3145</v>
       </c>
       <c r="D15" t="n">
         <v>1.7402</v>
@@ -1143,7 +1143,7 @@
         <v>5.2656</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>4.246</v>
       </c>
       <c r="D16" t="n">
         <v>1.7058</v>
@@ -1189,7 +1189,7 @@
         <v>4.9146</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>3.9629</v>
       </c>
       <c r="D17" t="n">
         <v>1.564</v>
@@ -1235,7 +1235,7 @@
         <v>4.8205</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>3.8871</v>
       </c>
       <c r="D18" t="n">
         <v>1.526</v>
@@ -1281,7 +1281,7 @@
         <v>4.7649</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>3.8422</v>
       </c>
       <c r="D19" t="n">
         <v>1.5036</v>
@@ -1327,7 +1327,7 @@
         <v>4.5656</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>3.6815</v>
       </c>
       <c r="D20" t="n">
         <v>1.423</v>
@@ -1373,7 +1373,7 @@
         <v>4.3274</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>3.4894</v>
       </c>
       <c r="D21" t="n">
         <v>1.3268</v>
@@ -1419,7 +1419,7 @@
         <v>4.3168</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>3.4809</v>
       </c>
       <c r="D22" t="n">
         <v>1.3225</v>
@@ -1465,7 +1465,7 @@
         <v>4.1883</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>3.3773</v>
       </c>
       <c r="D23" t="n">
         <v>1.2706</v>
@@ -1511,7 +1511,7 @@
         <v>4.0895</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>3.2976</v>
       </c>
       <c r="D24" t="n">
         <v>1.2307</v>
@@ -1557,7 +1557,7 @@
         <v>4.0665</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>3.2791</v>
       </c>
       <c r="D25" t="n">
         <v>1.2214</v>
@@ -1603,7 +1603,7 @@
         <v>4.0537</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>3.2687</v>
       </c>
       <c r="D26" t="n">
         <v>1.2162</v>
@@ -1649,7 +1649,7 @@
         <v>3.9929</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>3.2197</v>
       </c>
       <c r="D27" t="n">
         <v>1.1917</v>
@@ -1695,7 +1695,7 @@
         <v>3.9896</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>3.2171</v>
       </c>
       <c r="D28" t="n">
         <v>1.1903</v>
@@ -1741,7 +1741,7 @@
         <v>3.8238</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>3.0834</v>
       </c>
       <c r="D29" t="n">
         <v>1.1234</v>
@@ -1787,7 +1787,7 @@
         <v>3.6735</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>2.9622</v>
       </c>
       <c r="D30" t="n">
         <v>1.0627</v>
@@ -1833,7 +1833,7 @@
         <v>3.6464</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>2.9403</v>
       </c>
       <c r="D31" t="n">
         <v>1.0517</v>
@@ -1879,7 +1879,7 @@
         <v>3.5501</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>2.8627</v>
       </c>
       <c r="D32" t="n">
         <v>1.0128</v>
@@ -1925,7 +1925,7 @@
         <v>3.5224</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>2.8403</v>
       </c>
       <c r="D33" t="n">
         <v>1.0016</v>
@@ -1971,7 +1971,7 @@
         <v>3.4607</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>2.7906</v>
       </c>
       <c r="D34" t="n">
         <v>0.9767</v>
@@ -2017,7 +2017,7 @@
         <v>3.4268</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>2.7632</v>
       </c>
       <c r="D35" t="n">
         <v>0.963</v>
@@ -2063,7 +2063,7 @@
         <v>3.0894</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>2.4912</v>
       </c>
       <c r="D36" t="n">
         <v>0.8267</v>
@@ -2109,7 +2109,7 @@
         <v>3.0275</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>2.4413</v>
       </c>
       <c r="D37" t="n">
         <v>0.8017</v>
@@ -2155,7 +2155,7 @@
         <v>2.9782</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>2.4015</v>
       </c>
       <c r="D38" t="n">
         <v>0.7818000000000001</v>
@@ -2201,7 +2201,7 @@
         <v>2.9094</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>2.346</v>
       </c>
       <c r="D39" t="n">
         <v>0.754</v>
@@ -2247,7 +2247,7 @@
         <v>2.7654</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>2.2299</v>
       </c>
       <c r="D40" t="n">
         <v>0.6958</v>
@@ -2293,7 +2293,7 @@
         <v>2.7348</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>2.2052</v>
       </c>
       <c r="D41" t="n">
         <v>0.6834</v>
@@ -2339,7 +2339,7 @@
         <v>2.68</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>2.161</v>
       </c>
       <c r="D42" t="n">
         <v>0.6613</v>
@@ -2385,7 +2385,7 @@
         <v>2.6334</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>2.1235</v>
       </c>
       <c r="D43" t="n">
         <v>0.6425</v>
@@ -2431,7 +2431,7 @@
         <v>2.6187</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>2.1116</v>
       </c>
       <c r="D44" t="n">
         <v>0.6365</v>
@@ -2477,7 +2477,7 @@
         <v>2.5921</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>2.0902</v>
       </c>
       <c r="D45" t="n">
         <v>0.6258</v>
@@ -2523,7 +2523,7 @@
         <v>2.5642</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>2.0677</v>
       </c>
       <c r="D46" t="n">
         <v>0.6145</v>
@@ -2569,7 +2569,7 @@
         <v>2.5146</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>2.0277</v>
       </c>
       <c r="D47" t="n">
         <v>0.5945</v>
@@ -2615,7 +2615,7 @@
         <v>2.4877</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>2.006</v>
       </c>
       <c r="D48" t="n">
         <v>0.5836</v>
@@ -2661,7 +2661,7 @@
         <v>2.475</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>1.9957</v>
       </c>
       <c r="D49" t="n">
         <v>0.5785</v>
@@ -2707,7 +2707,7 @@
         <v>2.4622</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>1.9854</v>
       </c>
       <c r="D50" t="n">
         <v>0.5733</v>
@@ -2753,7 +2753,7 @@
         <v>2.4033</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>1.9379</v>
       </c>
       <c r="D51" t="n">
         <v>0.5495</v>
@@ -2799,7 +2799,7 @@
         <v>2.3554</v>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>1.8993</v>
       </c>
       <c r="D52" t="n">
         <v>0.5302</v>
@@ -2845,7 +2845,7 @@
         <v>2.3439</v>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="D53" t="n">
         <v>0.5255</v>
@@ -2891,7 +2891,7 @@
         <v>2.3271</v>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>1.8765</v>
       </c>
       <c r="D54" t="n">
         <v>0.5187</v>
@@ -2937,7 +2937,7 @@
         <v>2.2325</v>
       </c>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>1.8002</v>
       </c>
       <c r="D55" t="n">
         <v>0.4805</v>
@@ -2983,7 +2983,7 @@
         <v>2.1877</v>
       </c>
       <c r="C56" t="n">
-        <v>0</v>
+        <v>1.7641</v>
       </c>
       <c r="D56" t="n">
         <v>0.4624</v>
@@ -3029,7 +3029,7 @@
         <v>2.0579</v>
       </c>
       <c r="C57" t="n">
-        <v>0</v>
+        <v>1.6594</v>
       </c>
       <c r="D57" t="n">
         <v>0.41</v>
@@ -3075,7 +3075,7 @@
         <v>2.0396</v>
       </c>
       <c r="C58" t="n">
-        <v>0</v>
+        <v>1.6447</v>
       </c>
       <c r="D58" t="n">
         <v>0.4026</v>
@@ -3121,7 +3121,7 @@
         <v>1.9924</v>
       </c>
       <c r="C59" t="n">
-        <v>0</v>
+        <v>1.6066</v>
       </c>
       <c r="D59" t="n">
         <v>0.3835</v>
@@ -3167,7 +3167,7 @@
         <v>1.9669</v>
       </c>
       <c r="C60" t="n">
-        <v>0</v>
+        <v>1.586</v>
       </c>
       <c r="D60" t="n">
         <v>0.3732</v>
@@ -3213,7 +3213,7 @@
         <v>1.8967</v>
       </c>
       <c r="C61" t="n">
-        <v>0</v>
+        <v>1.5294</v>
       </c>
       <c r="D61" t="n">
         <v>0.3449</v>
@@ -3259,7 +3259,7 @@
         <v>1.8373</v>
       </c>
       <c r="C62" t="n">
-        <v>0</v>
+        <v>1.4815</v>
       </c>
       <c r="D62" t="n">
         <v>0.3209</v>
@@ -3305,7 +3305,7 @@
         <v>1.7823</v>
       </c>
       <c r="C63" t="n">
-        <v>0</v>
+        <v>1.4372</v>
       </c>
       <c r="D63" t="n">
         <v>0.2986</v>
@@ -3351,7 +3351,7 @@
         <v>1.7224</v>
       </c>
       <c r="C64" t="n">
-        <v>0</v>
+        <v>1.3889</v>
       </c>
       <c r="D64" t="n">
         <v>0.2744</v>
@@ -3397,7 +3397,7 @@
         <v>1.7048</v>
       </c>
       <c r="C65" t="n">
-        <v>0</v>
+        <v>1.3747</v>
       </c>
       <c r="D65" t="n">
         <v>0.2673</v>
@@ -3443,7 +3443,7 @@
         <v>1.6268</v>
       </c>
       <c r="C66" t="n">
-        <v>0</v>
+        <v>1.3118</v>
       </c>
       <c r="D66" t="n">
         <v>0.2358</v>
@@ -3489,7 +3489,7 @@
         <v>1.5021</v>
       </c>
       <c r="C67" t="n">
-        <v>0</v>
+        <v>1.2112</v>
       </c>
       <c r="D67" t="n">
         <v>0.1855</v>
@@ -3535,7 +3535,7 @@
         <v>1.4843</v>
       </c>
       <c r="C68" t="n">
-        <v>0</v>
+        <v>1.1969</v>
       </c>
       <c r="D68" t="n">
         <v>0.1783</v>
@@ -3581,7 +3581,7 @@
         <v>1.4794</v>
       </c>
       <c r="C69" t="n">
-        <v>0</v>
+        <v>1.1929</v>
       </c>
       <c r="D69" t="n">
         <v>0.1763</v>
@@ -3627,7 +3627,7 @@
         <v>1.4668</v>
       </c>
       <c r="C70" t="n">
-        <v>0</v>
+        <v>1.1828</v>
       </c>
       <c r="D70" t="n">
         <v>0.1712</v>
@@ -3673,7 +3673,7 @@
         <v>1.4522</v>
       </c>
       <c r="C71" t="n">
-        <v>0</v>
+        <v>1.171</v>
       </c>
       <c r="D71" t="n">
         <v>0.1653</v>
@@ -3719,7 +3719,7 @@
         <v>1.3538</v>
       </c>
       <c r="C72" t="n">
-        <v>0</v>
+        <v>1.0916</v>
       </c>
       <c r="D72" t="n">
         <v>0.1255</v>
@@ -3765,7 +3765,7 @@
         <v>1.332</v>
       </c>
       <c r="C73" t="n">
-        <v>0</v>
+        <v>1.0741</v>
       </c>
       <c r="D73" t="n">
         <v>0.1167</v>
@@ -3811,7 +3811,7 @@
         <v>1.3284</v>
       </c>
       <c r="C74" t="n">
-        <v>0</v>
+        <v>1.0712</v>
       </c>
       <c r="D74" t="n">
         <v>0.1153</v>
@@ -3857,7 +3857,7 @@
         <v>1.2938</v>
       </c>
       <c r="C75" t="n">
-        <v>0</v>
+        <v>1.0433</v>
       </c>
       <c r="D75" t="n">
         <v>0.1013</v>
@@ -3903,7 +3903,7 @@
         <v>1.1753</v>
       </c>
       <c r="C76" t="n">
-        <v>0</v>
+        <v>0.9477</v>
       </c>
       <c r="D76" t="n">
         <v>0.0534</v>
@@ -3949,7 +3949,7 @@
         <v>1.1564</v>
       </c>
       <c r="C77" t="n">
-        <v>0</v>
+        <v>0.9325</v>
       </c>
       <c r="D77" t="n">
         <v>0.0458</v>
@@ -3995,7 +3995,7 @@
         <v>1.0993</v>
       </c>
       <c r="C78" t="n">
-        <v>0</v>
+        <v>0.8864</v>
       </c>
       <c r="D78" t="n">
         <v>0.0227</v>
@@ -4041,7 +4041,7 @@
         <v>1.0973</v>
       </c>
       <c r="C79" t="n">
-        <v>0</v>
+        <v>0.8848</v>
       </c>
       <c r="D79" t="n">
         <v>0.0219</v>
@@ -4087,7 +4087,7 @@
         <v>1.0523</v>
       </c>
       <c r="C80" t="n">
-        <v>0</v>
+        <v>0.8485</v>
       </c>
       <c r="D80" t="n">
         <v>0.0037</v>
@@ -4133,7 +4133,7 @@
         <v>1.0405</v>
       </c>
       <c r="C81" t="n">
-        <v>0</v>
+        <v>0.839</v>
       </c>
       <c r="D81" t="n">
         <v>-0.001</v>
@@ -4179,7 +4179,7 @@
         <v>1.0106</v>
       </c>
       <c r="C82" t="n">
-        <v>0</v>
+        <v>0.8149</v>
       </c>
       <c r="D82" t="n">
         <v>-0.0131</v>
@@ -4225,7 +4225,7 @@
         <v>0.9902</v>
       </c>
       <c r="C83" t="n">
-        <v>0</v>
+        <v>0.7985</v>
       </c>
       <c r="D83" t="n">
         <v>-0.0213</v>
@@ -4271,7 +4271,7 @@
         <v>0.8193</v>
       </c>
       <c r="C84" t="n">
-        <v>0</v>
+        <v>0.6607</v>
       </c>
       <c r="D84" t="n">
         <v>-0.09039999999999999</v>
@@ -4317,7 +4317,7 @@
         <v>0.7036</v>
       </c>
       <c r="C85" t="n">
-        <v>0</v>
+        <v>0.5674</v>
       </c>
       <c r="D85" t="n">
         <v>-0.1371</v>
@@ -4363,7 +4363,7 @@
         <v>0.6928</v>
       </c>
       <c r="C86" t="n">
-        <v>0</v>
+        <v>0.5586</v>
       </c>
       <c r="D86" t="n">
         <v>-0.1415</v>
@@ -4409,7 +4409,7 @@
         <v>0.6152</v>
       </c>
       <c r="C87" t="n">
-        <v>0</v>
+        <v>0.4961</v>
       </c>
       <c r="D87" t="n">
         <v>-0.1728</v>
@@ -4455,7 +4455,7 @@
         <v>0.5711000000000001</v>
       </c>
       <c r="C88" t="n">
-        <v>0</v>
+        <v>0.4605</v>
       </c>
       <c r="D88" t="n">
         <v>-0.1907</v>
@@ -4501,7 +4501,7 @@
         <v>0.5514</v>
       </c>
       <c r="C89" t="n">
-        <v>0</v>
+        <v>0.4446</v>
       </c>
       <c r="D89" t="n">
         <v>-0.1986</v>
@@ -4547,7 +4547,7 @@
         <v>0.5272</v>
       </c>
       <c r="C90" t="n">
-        <v>0</v>
+        <v>0.4251</v>
       </c>
       <c r="D90" t="n">
         <v>-0.2084</v>
@@ -4593,7 +4593,7 @@
         <v>0.502</v>
       </c>
       <c r="C91" t="n">
-        <v>0</v>
+        <v>0.4048</v>
       </c>
       <c r="D91" t="n">
         <v>-0.2186</v>
@@ -4639,7 +4639,7 @@
         <v>0.4456</v>
       </c>
       <c r="C92" t="n">
-        <v>0</v>
+        <v>0.3593</v>
       </c>
       <c r="D92" t="n">
         <v>-0.2413</v>
@@ -4685,7 +4685,7 @@
         <v>0.4298</v>
       </c>
       <c r="C93" t="n">
-        <v>0</v>
+        <v>0.3466</v>
       </c>
       <c r="D93" t="n">
         <v>-0.2477</v>
@@ -4731,7 +4731,7 @@
         <v>0.4125</v>
       </c>
       <c r="C94" t="n">
-        <v>0</v>
+        <v>0.3326</v>
       </c>
       <c r="D94" t="n">
         <v>-0.2547</v>
@@ -4777,7 +4777,7 @@
         <v>0.4074</v>
       </c>
       <c r="C95" t="n">
-        <v>0</v>
+        <v>0.3285</v>
       </c>
       <c r="D95" t="n">
         <v>-0.2568</v>
@@ -4823,7 +4823,7 @@
         <v>0.3903</v>
       </c>
       <c r="C96" t="n">
-        <v>0</v>
+        <v>0.3147</v>
       </c>
       <c r="D96" t="n">
         <v>-0.2637</v>
@@ -4869,7 +4869,7 @@
         <v>0.3605</v>
       </c>
       <c r="C97" t="n">
-        <v>0</v>
+        <v>0.2907</v>
       </c>
       <c r="D97" t="n">
         <v>-0.2757</v>
@@ -4915,7 +4915,7 @@
         <v>0.2705</v>
       </c>
       <c r="C98" t="n">
-        <v>0</v>
+        <v>0.2181</v>
       </c>
       <c r="D98" t="n">
         <v>-0.3121</v>
@@ -4961,7 +4961,7 @@
         <v>0.2575</v>
       </c>
       <c r="C99" t="n">
-        <v>0</v>
+        <v>0.2076</v>
       </c>
       <c r="D99" t="n">
         <v>-0.3173</v>
@@ -5007,7 +5007,7 @@
         <v>0.2488</v>
       </c>
       <c r="C100" t="n">
-        <v>0</v>
+        <v>0.2006</v>
       </c>
       <c r="D100" t="n">
         <v>-0.3209</v>
@@ -5053,7 +5053,7 @@
         <v>0.2308</v>
       </c>
       <c r="C101" t="n">
-        <v>0</v>
+        <v>0.1861</v>
       </c>
       <c r="D101" t="n">
         <v>-0.3281</v>
@@ -5099,7 +5099,7 @@
         <v>0.1835</v>
       </c>
       <c r="C102" t="n">
-        <v>0</v>
+        <v>0.148</v>
       </c>
       <c r="D102" t="n">
         <v>-0.3472</v>
@@ -5145,7 +5145,7 @@
         <v>0.12</v>
       </c>
       <c r="C103" t="n">
-        <v>0</v>
+        <v>0.0968</v>
       </c>
       <c r="D103" t="n">
         <v>-0.3729</v>
@@ -5191,7 +5191,7 @@
         <v>0.0998</v>
       </c>
       <c r="C104" t="n">
-        <v>0</v>
+        <v>0.0805</v>
       </c>
       <c r="D104" t="n">
         <v>-0.381</v>
@@ -5237,7 +5237,7 @@
         <v>0.09</v>
       </c>
       <c r="C105" t="n">
-        <v>0</v>
+        <v>0.0726</v>
       </c>
       <c r="D105" t="n">
         <v>-0.385</v>
@@ -5283,7 +5283,7 @@
         <v>-0.0161</v>
       </c>
       <c r="C106" t="n">
-        <v>-0</v>
+        <v>-0.013</v>
       </c>
       <c r="D106" t="n">
         <v>-0.4279</v>
@@ -5329,7 +5329,7 @@
         <v>-0.09760000000000001</v>
       </c>
       <c r="C107" t="n">
-        <v>-0</v>
+        <v>-0.07870000000000001</v>
       </c>
       <c r="D107" t="n">
         <v>-0.4608</v>
@@ -5375,7 +5375,7 @@
         <v>-0.1123</v>
       </c>
       <c r="C108" t="n">
-        <v>-0</v>
+        <v>-0.0906</v>
       </c>
       <c r="D108" t="n">
         <v>-0.4667</v>
@@ -5421,7 +5421,7 @@
         <v>-0.1139</v>
       </c>
       <c r="C109" t="n">
-        <v>-0</v>
+        <v>-0.09180000000000001</v>
       </c>
       <c r="D109" t="n">
         <v>-0.4674</v>
@@ -5467,7 +5467,7 @@
         <v>-0.141</v>
       </c>
       <c r="C110" t="n">
-        <v>-0</v>
+        <v>-0.1137</v>
       </c>
       <c r="D110" t="n">
         <v>-0.4783</v>
@@ -5513,7 +5513,7 @@
         <v>-0.1462</v>
       </c>
       <c r="C111" t="n">
-        <v>-0</v>
+        <v>-0.1179</v>
       </c>
       <c r="D111" t="n">
         <v>-0.4804</v>
@@ -5559,7 +5559,7 @@
         <v>-0.1527</v>
       </c>
       <c r="C112" t="n">
-        <v>-0</v>
+        <v>-0.1231</v>
       </c>
       <c r="D112" t="n">
         <v>-0.483</v>
@@ -5605,7 +5605,7 @@
         <v>-0.1785</v>
       </c>
       <c r="C113" t="n">
-        <v>-0</v>
+        <v>-0.1439</v>
       </c>
       <c r="D113" t="n">
         <v>-0.4935</v>
@@ -5651,7 +5651,7 @@
         <v>-0.2163</v>
       </c>
       <c r="C114" t="n">
-        <v>-0</v>
+        <v>-0.1744</v>
       </c>
       <c r="D114" t="n">
         <v>-0.5087</v>
@@ -5697,7 +5697,7 @@
         <v>-0.2637</v>
       </c>
       <c r="C115" t="n">
-        <v>-0</v>
+        <v>-0.2126</v>
       </c>
       <c r="D115" t="n">
         <v>-0.5279</v>
@@ -5743,7 +5743,7 @@
         <v>-0.3427</v>
       </c>
       <c r="C116" t="n">
-        <v>-0</v>
+        <v>-0.2763</v>
       </c>
       <c r="D116" t="n">
         <v>-0.5598</v>
@@ -5789,7 +5789,7 @@
         <v>-0.3694</v>
       </c>
       <c r="C117" t="n">
-        <v>-0</v>
+        <v>-0.2979</v>
       </c>
       <c r="D117" t="n">
         <v>-0.5706</v>
@@ -5835,7 +5835,7 @@
         <v>-0.4683</v>
       </c>
       <c r="C118" t="n">
-        <v>-0</v>
+        <v>-0.3776</v>
       </c>
       <c r="D118" t="n">
         <v>-0.6105</v>
@@ -5881,7 +5881,7 @@
         <v>-0.4817</v>
       </c>
       <c r="C119" t="n">
-        <v>-0</v>
+        <v>-0.3884</v>
       </c>
       <c r="D119" t="n">
         <v>-0.616</v>
@@ -5927,7 +5927,7 @@
         <v>-0.5723</v>
       </c>
       <c r="C120" t="n">
-        <v>-0</v>
+        <v>-0.4615</v>
       </c>
       <c r="D120" t="n">
         <v>-0.6526</v>
@@ -5973,7 +5973,7 @@
         <v>-0.6074000000000001</v>
       </c>
       <c r="C121" t="n">
-        <v>-0</v>
+        <v>-0.4898</v>
       </c>
       <c r="D121" t="n">
         <v>-0.6667</v>
@@ -6019,7 +6019,7 @@
         <v>-0.6776</v>
       </c>
       <c r="C122" t="n">
-        <v>-0</v>
+        <v>-0.5464</v>
       </c>
       <c r="D122" t="n">
         <v>-0.6951000000000001</v>
@@ -6065,7 +6065,7 @@
         <v>-0.6915</v>
       </c>
       <c r="C123" t="n">
-        <v>-0</v>
+        <v>-0.5576</v>
       </c>
       <c r="D123" t="n">
         <v>-0.7007</v>
@@ -6111,7 +6111,7 @@
         <v>-0.7004</v>
       </c>
       <c r="C124" t="n">
-        <v>-0</v>
+        <v>-0.5648</v>
       </c>
       <c r="D124" t="n">
         <v>-0.7043</v>
@@ -6157,7 +6157,7 @@
         <v>-0.7121</v>
       </c>
       <c r="C125" t="n">
-        <v>-0</v>
+        <v>-0.5742</v>
       </c>
       <c r="D125" t="n">
         <v>-0.709</v>
@@ -6203,7 +6203,7 @@
         <v>-0.7146</v>
       </c>
       <c r="C126" t="n">
-        <v>-0</v>
+        <v>-0.5762</v>
       </c>
       <c r="D126" t="n">
         <v>-0.71</v>
@@ -6249,7 +6249,7 @@
         <v>-0.7532</v>
       </c>
       <c r="C127" t="n">
-        <v>-0</v>
+        <v>-0.6073</v>
       </c>
       <c r="D127" t="n">
         <v>-0.7256</v>
@@ -6295,7 +6295,7 @@
         <v>-0.7844</v>
       </c>
       <c r="C128" t="n">
-        <v>-0</v>
+        <v>-0.6325</v>
       </c>
       <c r="D128" t="n">
         <v>-0.7382</v>
@@ -6341,7 +6341,7 @@
         <v>-0.8068</v>
       </c>
       <c r="C129" t="n">
-        <v>-0</v>
+        <v>-0.6506</v>
       </c>
       <c r="D129" t="n">
         <v>-0.7473</v>
@@ -6387,7 +6387,7 @@
         <v>-0.8414</v>
       </c>
       <c r="C130" t="n">
-        <v>-0</v>
+        <v>-0.6785</v>
       </c>
       <c r="D130" t="n">
         <v>-0.7613</v>
@@ -6433,7 +6433,7 @@
         <v>-0.8426</v>
       </c>
       <c r="C131" t="n">
-        <v>-0</v>
+        <v>-0.6794</v>
       </c>
       <c r="D131" t="n">
         <v>-0.7618</v>
@@ -6479,7 +6479,7 @@
         <v>-0.9557</v>
       </c>
       <c r="C132" t="n">
-        <v>-0</v>
+        <v>-0.7706</v>
       </c>
       <c r="D132" t="n">
         <v>-0.8074</v>
@@ -6525,7 +6525,7 @@
         <v>-1.018</v>
       </c>
       <c r="C133" t="n">
-        <v>-0</v>
+        <v>-0.8209</v>
       </c>
       <c r="D133" t="n">
         <v>-0.8326</v>
@@ -6571,7 +6571,7 @@
         <v>-1.0808</v>
       </c>
       <c r="C134" t="n">
-        <v>-0</v>
+        <v>-0.8715000000000001</v>
       </c>
       <c r="D134" t="n">
         <v>-0.858</v>
@@ -6617,7 +6617,7 @@
         <v>-1.1902</v>
       </c>
       <c r="C135" t="n">
-        <v>-0</v>
+        <v>-0.9597</v>
       </c>
       <c r="D135" t="n">
         <v>-0.9022</v>
@@ -6663,7 +6663,7 @@
         <v>-1.223</v>
       </c>
       <c r="C136" t="n">
-        <v>-0</v>
+        <v>-0.9862</v>
       </c>
       <c r="D136" t="n">
         <v>-0.9154</v>
@@ -6709,7 +6709,7 @@
         <v>-1.2894</v>
       </c>
       <c r="C137" t="n">
-        <v>-0</v>
+        <v>-1.0397</v>
       </c>
       <c r="D137" t="n">
         <v>-0.9423</v>
@@ -6755,7 +6755,7 @@
         <v>-1.4338</v>
       </c>
       <c r="C138" t="n">
-        <v>-0</v>
+        <v>-1.1562</v>
       </c>
       <c r="D138" t="n">
         <v>-1.0006</v>
@@ -6801,7 +6801,7 @@
         <v>-1.489</v>
       </c>
       <c r="C139" t="n">
-        <v>-0</v>
+        <v>-1.2007</v>
       </c>
       <c r="D139" t="n">
         <v>-1.0229</v>
@@ -6847,7 +6847,7 @@
         <v>-1.5373</v>
       </c>
       <c r="C140" t="n">
-        <v>-0</v>
+        <v>-1.2396</v>
       </c>
       <c r="D140" t="n">
         <v>-1.0424</v>
@@ -6893,7 +6893,7 @@
         <v>-1.5571</v>
       </c>
       <c r="C141" t="n">
-        <v>-0</v>
+        <v>-1.2556</v>
       </c>
       <c r="D141" t="n">
         <v>-1.0504</v>
@@ -6939,7 +6939,7 @@
         <v>-1.6623</v>
       </c>
       <c r="C142" t="n">
-        <v>-0</v>
+        <v>-1.3404</v>
       </c>
       <c r="D142" t="n">
         <v>-1.0929</v>
@@ -6985,7 +6985,7 @@
         <v>-1.7012</v>
       </c>
       <c r="C143" t="n">
-        <v>-0</v>
+        <v>-1.3718</v>
       </c>
       <c r="D143" t="n">
         <v>-1.1086</v>
@@ -7031,7 +7031,7 @@
         <v>-1.707</v>
       </c>
       <c r="C144" t="n">
-        <v>-0</v>
+        <v>-1.3765</v>
       </c>
       <c r="D144" t="n">
         <v>-1.111</v>
@@ -7077,7 +7077,7 @@
         <v>-1.7333</v>
       </c>
       <c r="C145" t="n">
-        <v>-0</v>
+        <v>-1.3977</v>
       </c>
       <c r="D145" t="n">
         <v>-1.1216</v>
@@ -7123,7 +7123,7 @@
         <v>-1.9122</v>
       </c>
       <c r="C146" t="n">
-        <v>-0</v>
+        <v>-1.5419</v>
       </c>
       <c r="D146" t="n">
         <v>-1.1938</v>
@@ -7169,7 +7169,7 @@
         <v>-1.9423</v>
       </c>
       <c r="C147" t="n">
-        <v>-0</v>
+        <v>-1.5662</v>
       </c>
       <c r="D147" t="n">
         <v>-1.206</v>
@@ -7215,7 +7215,7 @@
         <v>-2.0673</v>
       </c>
       <c r="C148" t="n">
-        <v>-0</v>
+        <v>-1.667</v>
       </c>
       <c r="D148" t="n">
         <v>-1.2565</v>
@@ -7261,7 +7261,7 @@
         <v>-2.1873</v>
       </c>
       <c r="C149" t="n">
-        <v>-0</v>
+        <v>-1.7638</v>
       </c>
       <c r="D149" t="n">
         <v>-1.305</v>
@@ -7307,7 +7307,7 @@
         <v>-2.2237</v>
       </c>
       <c r="C150" t="n">
-        <v>-0</v>
+        <v>-1.7931</v>
       </c>
       <c r="D150" t="n">
         <v>-1.3197</v>
@@ -7353,7 +7353,7 @@
         <v>-2.2804</v>
       </c>
       <c r="C151" t="n">
-        <v>-0</v>
+        <v>-1.8388</v>
       </c>
       <c r="D151" t="n">
         <v>-1.3426</v>
@@ -7399,7 +7399,7 @@
         <v>-2.4541</v>
       </c>
       <c r="C152" t="n">
-        <v>-0</v>
+        <v>-1.9789</v>
       </c>
       <c r="D152" t="n">
         <v>-1.4128</v>
@@ -7445,7 +7445,7 @@
         <v>-2.5029</v>
       </c>
       <c r="C153" t="n">
-        <v>-0</v>
+        <v>-2.0182</v>
       </c>
       <c r="D153" t="n">
         <v>-1.4325</v>
@@ -7491,7 +7491,7 @@
         <v>-2.583</v>
       </c>
       <c r="C154" t="n">
-        <v>-0</v>
+        <v>-2.0828</v>
       </c>
       <c r="D154" t="n">
         <v>-1.4648</v>
@@ -7537,7 +7537,7 @@
         <v>-2.5834</v>
       </c>
       <c r="C155" t="n">
-        <v>-0</v>
+        <v>-2.0831</v>
       </c>
       <c r="D155" t="n">
         <v>-1.465</v>
@@ -7583,7 +7583,7 @@
         <v>-2.5927</v>
       </c>
       <c r="C156" t="n">
-        <v>-0</v>
+        <v>-2.0906</v>
       </c>
       <c r="D156" t="n">
         <v>-1.4688</v>
@@ -7629,7 +7629,7 @@
         <v>-2.6291</v>
       </c>
       <c r="C157" t="n">
-        <v>-0</v>
+        <v>-2.12</v>
       </c>
       <c r="D157" t="n">
         <v>-1.4835</v>
@@ -7675,7 +7675,7 @@
         <v>-2.7327</v>
       </c>
       <c r="C158" t="n">
-        <v>-0</v>
+        <v>-2.2035</v>
       </c>
       <c r="D158" t="n">
         <v>-1.5253</v>
@@ -7721,7 +7721,7 @@
         <v>-2.778</v>
       </c>
       <c r="C159" t="n">
-        <v>-0</v>
+        <v>-2.2401</v>
       </c>
       <c r="D159" t="n">
         <v>-1.5436</v>
@@ -7767,7 +7767,7 @@
         <v>-3.1244</v>
       </c>
       <c r="C160" t="n">
-        <v>-0</v>
+        <v>-2.5194</v>
       </c>
       <c r="D160" t="n">
         <v>-1.6836</v>
@@ -7813,7 +7813,7 @@
         <v>-3.8555</v>
       </c>
       <c r="C161" t="n">
-        <v>-0</v>
+        <v>-3.1089</v>
       </c>
       <c r="D161" t="n">
         <v>-1.9789</v>
@@ -7859,7 +7859,7 @@
         <v>-4.7922</v>
       </c>
       <c r="C162" t="n">
-        <v>-0</v>
+        <v>-3.8642</v>
       </c>
       <c r="D162" t="n">
         <v>-2.3573</v>

--- a/database/event/6862/event_6862_evp_summary.xlsx
+++ b/database/event/6862/event_6862_evp_summary.xlsx
@@ -496,25 +496,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10.0996</v>
+        <v>10.0216</v>
       </c>
       <c r="C2" t="n">
-        <v>8.1439</v>
+        <v>8.081</v>
       </c>
       <c r="D2" t="n">
-        <v>3.6587</v>
+        <v>3.5487</v>
       </c>
       <c r="E2" t="n">
-        <v>10.0996</v>
+        <v>10.0216</v>
       </c>
       <c r="F2" t="n">
-        <v>3.5215</v>
+        <v>3.4434</v>
       </c>
       <c r="G2" t="n">
         <v>6.5782</v>
       </c>
       <c r="H2" t="n">
-        <v>3.5215</v>
+        <v>3.4434</v>
       </c>
       <c r="I2" t="n">
         <v>3.621</v>
@@ -542,25 +542,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.895799999999999</v>
+        <v>9.826000000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>7.9796</v>
+        <v>7.9233</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5763</v>
+        <v>3.4708</v>
       </c>
       <c r="E3" t="n">
-        <v>9.895799999999999</v>
+        <v>9.826000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>4.6153</v>
+        <v>4.5455</v>
       </c>
       <c r="G3" t="n">
         <v>5.2805</v>
       </c>
       <c r="H3" t="n">
-        <v>4.9337</v>
+        <v>4.8243</v>
       </c>
       <c r="I3" t="n">
         <v>5.0731</v>
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.3003</v>
+        <v>9.123100000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>7.4994</v>
+        <v>7.3565</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3358</v>
+        <v>3.1907</v>
       </c>
       <c r="E4" t="n">
-        <v>9.3003</v>
+        <v>9.123100000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>5.8685</v>
+        <v>5.6913</v>
       </c>
       <c r="G4" t="n">
         <v>3.4318</v>
       </c>
       <c r="H4" t="n">
-        <v>6.8987</v>
+        <v>6.6209</v>
       </c>
       <c r="I4" t="n">
         <v>7.2603</v>
@@ -634,25 +634,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.700799999999999</v>
+        <v>8.632400000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>7.016</v>
+        <v>6.9608</v>
       </c>
       <c r="D5" t="n">
-        <v>3.0936</v>
+        <v>2.9952</v>
       </c>
       <c r="E5" t="n">
-        <v>8.700799999999999</v>
+        <v>8.632400000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>4.5523</v>
+        <v>4.4839</v>
       </c>
       <c r="G5" t="n">
         <v>4.1485</v>
       </c>
       <c r="H5" t="n">
-        <v>4.8349</v>
+        <v>4.7277</v>
       </c>
       <c r="I5" t="n">
         <v>4.9715</v>
@@ -680,25 +680,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.279999999999999</v>
+        <v>8.227600000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>6.6767</v>
+        <v>6.6344</v>
       </c>
       <c r="D6" t="n">
-        <v>2.9236</v>
+        <v>2.834</v>
       </c>
       <c r="E6" t="n">
-        <v>8.279999999999999</v>
+        <v>8.227600000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>2.3617</v>
+        <v>2.3093</v>
       </c>
       <c r="G6" t="n">
         <v>5.9183</v>
       </c>
       <c r="H6" t="n">
-        <v>2.3617</v>
+        <v>2.3093</v>
       </c>
       <c r="I6" t="n">
         <v>2.4284</v>
@@ -726,25 +726,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.6107</v>
+        <v>6.5441</v>
       </c>
       <c r="C7" t="n">
-        <v>5.3306</v>
+        <v>5.2769</v>
       </c>
       <c r="D7" t="n">
-        <v>2.2492</v>
+        <v>2.1633</v>
       </c>
       <c r="E7" t="n">
-        <v>6.6107</v>
+        <v>6.5441</v>
       </c>
       <c r="F7" t="n">
-        <v>4.471</v>
+        <v>4.4044</v>
       </c>
       <c r="G7" t="n">
         <v>2.1397</v>
       </c>
       <c r="H7" t="n">
-        <v>4.7075</v>
+        <v>4.6031</v>
       </c>
       <c r="I7" t="n">
         <v>4.8405</v>
@@ -772,25 +772,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.343</v>
+        <v>6.1793</v>
       </c>
       <c r="C8" t="n">
-        <v>5.1147</v>
+        <v>4.9827</v>
       </c>
       <c r="D8" t="n">
-        <v>2.1411</v>
+        <v>2.0179</v>
       </c>
       <c r="E8" t="n">
-        <v>6.343</v>
+        <v>6.1793</v>
       </c>
       <c r="F8" t="n">
-        <v>5.532</v>
+        <v>5.3683</v>
       </c>
       <c r="G8" t="n">
         <v>0.8110000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>6.3711</v>
+        <v>6.1144</v>
       </c>
       <c r="I8" t="n">
         <v>6.705</v>
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.2315</v>
+        <v>6.1682</v>
       </c>
       <c r="C9" t="n">
-        <v>5.0248</v>
+        <v>4.9738</v>
       </c>
       <c r="D9" t="n">
-        <v>2.096</v>
+        <v>2.0135</v>
       </c>
       <c r="E9" t="n">
-        <v>6.2315</v>
+        <v>6.1682</v>
       </c>
       <c r="F9" t="n">
-        <v>4.3212</v>
+        <v>4.2579</v>
       </c>
       <c r="G9" t="n">
         <v>1.9103</v>
       </c>
       <c r="H9" t="n">
-        <v>4.4726</v>
+        <v>4.3734</v>
       </c>
       <c r="I9" t="n">
         <v>4.5989</v>
@@ -864,25 +864,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.7488</v>
+        <v>5.6764</v>
       </c>
       <c r="C10" t="n">
-        <v>4.6356</v>
+        <v>4.5772</v>
       </c>
       <c r="D10" t="n">
-        <v>1.901</v>
+        <v>1.8176</v>
       </c>
       <c r="E10" t="n">
-        <v>5.7488</v>
+        <v>5.6764</v>
       </c>
       <c r="F10" t="n">
-        <v>4.7305</v>
+        <v>4.6581</v>
       </c>
       <c r="G10" t="n">
         <v>1.0183</v>
       </c>
       <c r="H10" t="n">
-        <v>5.1143</v>
+        <v>5.0009</v>
       </c>
       <c r="I10" t="n">
         <v>5.2588</v>
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.6587</v>
+        <v>5.5201</v>
       </c>
       <c r="C11" t="n">
-        <v>4.5629</v>
+        <v>4.4512</v>
       </c>
       <c r="D11" t="n">
-        <v>1.8646</v>
+        <v>1.7553</v>
       </c>
       <c r="E11" t="n">
-        <v>5.6587</v>
+        <v>5.5201</v>
       </c>
       <c r="F11" t="n">
-        <v>5.6587</v>
+        <v>5.5201</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>6.5698</v>
+        <v>6.3525</v>
       </c>
       <c r="I11" t="n">
         <v>6.8502</v>
@@ -956,25 +956,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.6555</v>
+        <v>5.517</v>
       </c>
       <c r="C12" t="n">
-        <v>4.5604</v>
+        <v>4.4487</v>
       </c>
       <c r="D12" t="n">
-        <v>1.8633</v>
+        <v>1.7541</v>
       </c>
       <c r="E12" t="n">
-        <v>5.6555</v>
+        <v>5.517</v>
       </c>
       <c r="F12" t="n">
-        <v>5.6555</v>
+        <v>5.517</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>6.5647</v>
+        <v>6.3476</v>
       </c>
       <c r="I12" t="n">
         <v>6.8449</v>
@@ -1002,25 +1002,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.5666</v>
+        <v>5.4459</v>
       </c>
       <c r="C13" t="n">
-        <v>4.4887</v>
+        <v>4.3914</v>
       </c>
       <c r="D13" t="n">
-        <v>1.8274</v>
+        <v>1.7257</v>
       </c>
       <c r="E13" t="n">
-        <v>5.5666</v>
+        <v>5.4459</v>
       </c>
       <c r="F13" t="n">
-        <v>5.5666</v>
+        <v>5.4459</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>6.4254</v>
+        <v>6.2361</v>
       </c>
       <c r="I13" t="n">
         <v>6.6686</v>
@@ -1048,25 +1048,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.4865</v>
+        <v>5.4272</v>
       </c>
       <c r="C14" t="n">
-        <v>4.4241</v>
+        <v>4.3763</v>
       </c>
       <c r="D14" t="n">
-        <v>1.7951</v>
+        <v>1.7183</v>
       </c>
       <c r="E14" t="n">
-        <v>5.4865</v>
+        <v>5.4272</v>
       </c>
       <c r="F14" t="n">
-        <v>4.1439</v>
+        <v>4.0846</v>
       </c>
       <c r="G14" t="n">
         <v>1.3426</v>
       </c>
       <c r="H14" t="n">
-        <v>4.1946</v>
+        <v>4.1016</v>
       </c>
       <c r="I14" t="n">
         <v>4.3131</v>
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.3506</v>
+        <v>5.2222</v>
       </c>
       <c r="C15" t="n">
-        <v>4.3145</v>
+        <v>4.211</v>
       </c>
       <c r="D15" t="n">
-        <v>1.7402</v>
+        <v>1.6366</v>
       </c>
       <c r="E15" t="n">
-        <v>5.3506</v>
+        <v>5.2222</v>
       </c>
       <c r="F15" t="n">
-        <v>5.3506</v>
+        <v>5.2222</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>6.0867</v>
+        <v>5.8854</v>
       </c>
       <c r="I15" t="n">
         <v>6.3465</v>
@@ -1140,25 +1140,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.2656</v>
+        <v>5.1994</v>
       </c>
       <c r="C16" t="n">
-        <v>4.246</v>
+        <v>4.1926</v>
       </c>
       <c r="D16" t="n">
-        <v>1.7058</v>
+        <v>1.6275</v>
       </c>
       <c r="E16" t="n">
-        <v>5.2656</v>
+        <v>5.1994</v>
       </c>
       <c r="F16" t="n">
-        <v>4.4552</v>
+        <v>4.389</v>
       </c>
       <c r="G16" t="n">
         <v>0.8104</v>
       </c>
       <c r="H16" t="n">
-        <v>4.6828</v>
+        <v>4.5789</v>
       </c>
       <c r="I16" t="n">
         <v>4.8151</v>
@@ -1186,25 +1186,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4.9146</v>
+        <v>4.813</v>
       </c>
       <c r="C17" t="n">
-        <v>3.9629</v>
+        <v>3.881</v>
       </c>
       <c r="D17" t="n">
-        <v>1.564</v>
+        <v>1.4736</v>
       </c>
       <c r="E17" t="n">
-        <v>4.9146</v>
+        <v>4.813</v>
       </c>
       <c r="F17" t="n">
-        <v>4.9146</v>
+        <v>4.813</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>5.4029</v>
+        <v>5.2438</v>
       </c>
       <c r="I17" t="n">
         <v>5.6074</v>
@@ -1228,93 +1228,93 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>SunPayus</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4.8205</v>
+        <v>4.6992</v>
       </c>
       <c r="C18" t="n">
-        <v>3.8871</v>
+        <v>3.7892</v>
       </c>
       <c r="D18" t="n">
-        <v>1.526</v>
+        <v>1.4283</v>
       </c>
       <c r="E18" t="n">
-        <v>4.8205</v>
+        <v>4.6992</v>
       </c>
       <c r="F18" t="n">
-        <v>4.5222</v>
+        <v>2.8968</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2983</v>
+        <v>1.8024</v>
       </c>
       <c r="H18" t="n">
-        <v>4.7877</v>
+        <v>2.8968</v>
       </c>
       <c r="I18" t="n">
-        <v>5.0386</v>
+        <v>3.0462</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2983</v>
+        <v>1.8024</v>
       </c>
       <c r="K18" t="n">
-        <v>417</v>
+        <v>228</v>
       </c>
       <c r="L18" t="n">
-        <v>125</v>
+        <v>166</v>
       </c>
       <c r="M18" t="n">
-        <v>5.3369</v>
+        <v>4.848599999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>542</v>
+        <v>394</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SunPayus</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.7649</v>
+        <v>4.6975</v>
       </c>
       <c r="C19" t="n">
-        <v>3.8422</v>
+        <v>3.7879</v>
       </c>
       <c r="D19" t="n">
-        <v>1.5036</v>
+        <v>1.4276</v>
       </c>
       <c r="E19" t="n">
-        <v>4.7649</v>
+        <v>4.6975</v>
       </c>
       <c r="F19" t="n">
-        <v>2.9625</v>
+        <v>4.3992</v>
       </c>
       <c r="G19" t="n">
-        <v>1.8024</v>
+        <v>0.2983</v>
       </c>
       <c r="H19" t="n">
-        <v>2.9625</v>
+        <v>4.5948</v>
       </c>
       <c r="I19" t="n">
-        <v>3.0462</v>
+        <v>5.0386</v>
       </c>
       <c r="J19" t="n">
-        <v>1.8024</v>
+        <v>0.2983</v>
       </c>
       <c r="K19" t="n">
-        <v>228</v>
+        <v>417</v>
       </c>
       <c r="L19" t="n">
-        <v>166</v>
+        <v>125</v>
       </c>
       <c r="M19" t="n">
-        <v>4.848599999999999</v>
+        <v>5.3369</v>
       </c>
       <c r="N19" t="n">
-        <v>394</v>
+        <v>542</v>
       </c>
     </row>
     <row r="20">
@@ -1324,25 +1324,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.5656</v>
+        <v>4.5051</v>
       </c>
       <c r="C20" t="n">
-        <v>3.6815</v>
+        <v>3.6327</v>
       </c>
       <c r="D20" t="n">
-        <v>1.423</v>
+        <v>1.3509</v>
       </c>
       <c r="E20" t="n">
-        <v>4.5656</v>
+        <v>4.5051</v>
       </c>
       <c r="F20" t="n">
-        <v>4.197</v>
+        <v>4.1365</v>
       </c>
       <c r="G20" t="n">
         <v>0.3686</v>
       </c>
       <c r="H20" t="n">
-        <v>4.2779</v>
+        <v>4.1831</v>
       </c>
       <c r="I20" t="n">
         <v>4.3988</v>
@@ -1370,25 +1370,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4.3274</v>
+        <v>4.2329</v>
       </c>
       <c r="C21" t="n">
-        <v>3.4894</v>
+        <v>3.4132</v>
       </c>
       <c r="D21" t="n">
-        <v>1.3268</v>
+        <v>1.2425</v>
       </c>
       <c r="E21" t="n">
-        <v>4.3274</v>
+        <v>4.2329</v>
       </c>
       <c r="F21" t="n">
-        <v>4.3274</v>
+        <v>4.2329</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>4.4823</v>
+        <v>4.3341</v>
       </c>
       <c r="I21" t="n">
         <v>4.6736</v>
@@ -1416,25 +1416,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4.3168</v>
+        <v>4.1537</v>
       </c>
       <c r="C22" t="n">
-        <v>3.4809</v>
+        <v>3.3494</v>
       </c>
       <c r="D22" t="n">
-        <v>1.3225</v>
+        <v>1.2109</v>
       </c>
       <c r="E22" t="n">
-        <v>4.3168</v>
+        <v>4.1537</v>
       </c>
       <c r="F22" t="n">
-        <v>4.0484</v>
+        <v>3.8853</v>
       </c>
       <c r="G22" t="n">
         <v>0.2684</v>
       </c>
       <c r="H22" t="n">
-        <v>4.0484</v>
+        <v>3.8853</v>
       </c>
       <c r="I22" t="n">
         <v>4.2606</v>
@@ -1462,25 +1462,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4.1883</v>
+        <v>4.12</v>
       </c>
       <c r="C23" t="n">
-        <v>3.3773</v>
+        <v>3.3222</v>
       </c>
       <c r="D23" t="n">
-        <v>1.2706</v>
+        <v>1.1975</v>
       </c>
       <c r="E23" t="n">
-        <v>4.1883</v>
+        <v>4.12</v>
       </c>
       <c r="F23" t="n">
-        <v>4.5504</v>
+        <v>4.4821</v>
       </c>
       <c r="G23" t="n">
         <v>-0.3621</v>
       </c>
       <c r="H23" t="n">
-        <v>4.832</v>
+        <v>4.7248</v>
       </c>
       <c r="I23" t="n">
         <v>4.9685</v>
@@ -1504,231 +1504,231 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>saffee</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4.0895</v>
+        <v>3.9978</v>
       </c>
       <c r="C24" t="n">
-        <v>3.2976</v>
+        <v>3.2237</v>
       </c>
       <c r="D24" t="n">
-        <v>1.2307</v>
+        <v>1.1488</v>
       </c>
       <c r="E24" t="n">
-        <v>4.0895</v>
+        <v>3.9978</v>
       </c>
       <c r="F24" t="n">
-        <v>4.0895</v>
+        <v>3.9978</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>4.1093</v>
+        <v>3.9978</v>
       </c>
       <c r="I24" t="n">
-        <v>4.2649</v>
+        <v>4.1689</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>400</v>
+        <v>341</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>4.2649</v>
+        <v>4.1689</v>
       </c>
       <c r="N24" t="n">
-        <v>400</v>
+        <v>341</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>NertZ</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.0665</v>
+        <v>3.9929</v>
       </c>
       <c r="C25" t="n">
-        <v>3.2791</v>
+        <v>3.2197</v>
       </c>
       <c r="D25" t="n">
-        <v>1.2214</v>
+        <v>1.1469</v>
       </c>
       <c r="E25" t="n">
-        <v>4.0665</v>
+        <v>3.9929</v>
       </c>
       <c r="F25" t="n">
-        <v>4.0665</v>
+        <v>4.1477</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>-0.1548</v>
       </c>
       <c r="H25" t="n">
-        <v>4.0732</v>
+        <v>4.2005</v>
       </c>
       <c r="I25" t="n">
-        <v>4.1689</v>
+        <v>4.4172</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>-0.1548</v>
       </c>
       <c r="K25" t="n">
-        <v>341</v>
+        <v>228</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="M25" t="n">
-        <v>4.1689</v>
+        <v>4.2624</v>
       </c>
       <c r="N25" t="n">
-        <v>341</v>
+        <v>394</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>NertZ</t>
+          <t>saffee</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.0537</v>
+        <v>3.9883</v>
       </c>
       <c r="C26" t="n">
-        <v>3.2687</v>
+        <v>3.216</v>
       </c>
       <c r="D26" t="n">
-        <v>1.2162</v>
+        <v>1.145</v>
       </c>
       <c r="E26" t="n">
-        <v>4.0537</v>
+        <v>3.9883</v>
       </c>
       <c r="F26" t="n">
-        <v>4.2085</v>
+        <v>3.9883</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.1548</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>4.2958</v>
+        <v>3.9883</v>
       </c>
       <c r="I26" t="n">
-        <v>4.4172</v>
+        <v>4.2649</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.1548</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>228</v>
+        <v>400</v>
       </c>
       <c r="L26" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>4.2624</v>
+        <v>4.2649</v>
       </c>
       <c r="N26" t="n">
-        <v>394</v>
+        <v>400</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>XANTARES</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.9929</v>
+        <v>3.9158</v>
       </c>
       <c r="C27" t="n">
-        <v>3.2197</v>
+        <v>3.1575</v>
       </c>
       <c r="D27" t="n">
-        <v>1.1917</v>
+        <v>1.1161</v>
       </c>
       <c r="E27" t="n">
-        <v>3.9929</v>
+        <v>3.9158</v>
       </c>
       <c r="F27" t="n">
-        <v>3.9929</v>
+        <v>3.2507</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>0.6651</v>
       </c>
       <c r="H27" t="n">
-        <v>3.9929</v>
+        <v>3.2507</v>
       </c>
       <c r="I27" t="n">
-        <v>4.1057</v>
+        <v>3.4184</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>0.6651</v>
       </c>
       <c r="K27" t="n">
-        <v>329</v>
+        <v>195</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="M27" t="n">
-        <v>4.1057</v>
+        <v>4.0835</v>
       </c>
       <c r="N27" t="n">
-        <v>329</v>
+        <v>248</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>XANTARES</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3.9896</v>
+        <v>3.9043</v>
       </c>
       <c r="C28" t="n">
-        <v>3.2171</v>
+        <v>3.1483</v>
       </c>
       <c r="D28" t="n">
-        <v>1.1903</v>
+        <v>1.1116</v>
       </c>
       <c r="E28" t="n">
-        <v>3.9896</v>
+        <v>3.9043</v>
       </c>
       <c r="F28" t="n">
-        <v>3.3245</v>
+        <v>3.9043</v>
       </c>
       <c r="G28" t="n">
-        <v>0.6651</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>3.3245</v>
+        <v>3.9043</v>
       </c>
       <c r="I28" t="n">
-        <v>3.4184</v>
+        <v>4.1057</v>
       </c>
       <c r="J28" t="n">
-        <v>0.6651</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>195</v>
+        <v>329</v>
       </c>
       <c r="L28" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>4.0835</v>
+        <v>4.1057</v>
       </c>
       <c r="N28" t="n">
-        <v>248</v>
+        <v>329</v>
       </c>
     </row>
     <row r="29">
@@ -1738,25 +1738,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3.8238</v>
+        <v>3.739</v>
       </c>
       <c r="C29" t="n">
-        <v>3.0834</v>
+        <v>3.015</v>
       </c>
       <c r="D29" t="n">
-        <v>1.1234</v>
+        <v>1.0457</v>
       </c>
       <c r="E29" t="n">
-        <v>3.8238</v>
+        <v>3.739</v>
       </c>
       <c r="F29" t="n">
-        <v>3.8238</v>
+        <v>3.739</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>3.8238</v>
+        <v>3.739</v>
       </c>
       <c r="I29" t="n">
         <v>3.9318</v>
@@ -1784,25 +1784,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3.6735</v>
+        <v>3.5921</v>
       </c>
       <c r="C30" t="n">
-        <v>2.9622</v>
+        <v>2.8965</v>
       </c>
       <c r="D30" t="n">
-        <v>1.0627</v>
+        <v>0.9872</v>
       </c>
       <c r="E30" t="n">
-        <v>3.6735</v>
+        <v>3.5921</v>
       </c>
       <c r="F30" t="n">
-        <v>3.6735</v>
+        <v>3.5921</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>3.6735</v>
+        <v>3.5921</v>
       </c>
       <c r="I30" t="n">
         <v>3.7773</v>
@@ -1830,25 +1830,25 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3.6464</v>
+        <v>3.539</v>
       </c>
       <c r="C31" t="n">
-        <v>2.9403</v>
+        <v>2.8537</v>
       </c>
       <c r="D31" t="n">
-        <v>1.0517</v>
+        <v>0.966</v>
       </c>
       <c r="E31" t="n">
-        <v>3.6464</v>
+        <v>3.539</v>
       </c>
       <c r="F31" t="n">
-        <v>3.6464</v>
+        <v>3.539</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>3.6464</v>
+        <v>3.539</v>
       </c>
       <c r="I31" t="n">
         <v>3.7844</v>
@@ -1876,25 +1876,25 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3.5501</v>
+        <v>3.4872</v>
       </c>
       <c r="C32" t="n">
-        <v>2.8627</v>
+        <v>2.8119</v>
       </c>
       <c r="D32" t="n">
-        <v>1.0128</v>
+        <v>0.9454</v>
       </c>
       <c r="E32" t="n">
-        <v>3.5501</v>
+        <v>3.4872</v>
       </c>
       <c r="F32" t="n">
-        <v>2.8366</v>
+        <v>2.7737</v>
       </c>
       <c r="G32" t="n">
         <v>0.7135</v>
       </c>
       <c r="H32" t="n">
-        <v>2.8366</v>
+        <v>2.7737</v>
       </c>
       <c r="I32" t="n">
         <v>2.9168</v>
@@ -1922,25 +1922,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3.5224</v>
+        <v>3.4572</v>
       </c>
       <c r="C33" t="n">
-        <v>2.8403</v>
+        <v>2.7877</v>
       </c>
       <c r="D33" t="n">
-        <v>1.0016</v>
+        <v>0.9334</v>
       </c>
       <c r="E33" t="n">
-        <v>3.5224</v>
+        <v>3.4572</v>
       </c>
       <c r="F33" t="n">
-        <v>3.5224</v>
+        <v>3.4572</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>3.5224</v>
+        <v>3.4572</v>
       </c>
       <c r="I33" t="n">
         <v>3.6051</v>
@@ -1968,25 +1968,25 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3.4607</v>
+        <v>3.3587</v>
       </c>
       <c r="C34" t="n">
-        <v>2.7906</v>
+        <v>2.7083</v>
       </c>
       <c r="D34" t="n">
-        <v>0.9767</v>
+        <v>0.8942</v>
       </c>
       <c r="E34" t="n">
-        <v>3.4607</v>
+        <v>3.3587</v>
       </c>
       <c r="F34" t="n">
-        <v>3.4607</v>
+        <v>3.3587</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>3.4607</v>
+        <v>3.3587</v>
       </c>
       <c r="I34" t="n">
         <v>3.5916</v>
@@ -2014,25 +2014,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3.4268</v>
+        <v>3.3383</v>
       </c>
       <c r="C35" t="n">
-        <v>2.7632</v>
+        <v>2.6919</v>
       </c>
       <c r="D35" t="n">
-        <v>0.963</v>
+        <v>0.8861</v>
       </c>
       <c r="E35" t="n">
-        <v>3.4268</v>
+        <v>3.3383</v>
       </c>
       <c r="F35" t="n">
-        <v>3.4268</v>
+        <v>3.3383</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>3.4268</v>
+        <v>3.3383</v>
       </c>
       <c r="I35" t="n">
         <v>3.5401</v>
@@ -2060,25 +2060,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3.0894</v>
+        <v>3.0135</v>
       </c>
       <c r="C36" t="n">
-        <v>2.4912</v>
+        <v>2.43</v>
       </c>
       <c r="D36" t="n">
-        <v>0.8267</v>
+        <v>0.7567</v>
       </c>
       <c r="E36" t="n">
-        <v>3.0894</v>
+        <v>3.0135</v>
       </c>
       <c r="F36" t="n">
-        <v>3.425</v>
+        <v>3.3491</v>
       </c>
       <c r="G36" t="n">
         <v>-0.3356</v>
       </c>
       <c r="H36" t="n">
-        <v>3.425</v>
+        <v>3.3491</v>
       </c>
       <c r="I36" t="n">
         <v>3.5218</v>
@@ -2106,25 +2106,25 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3.0275</v>
+        <v>2.9604</v>
       </c>
       <c r="C37" t="n">
-        <v>2.4413</v>
+        <v>2.3871</v>
       </c>
       <c r="D37" t="n">
-        <v>0.8017</v>
+        <v>0.7355</v>
       </c>
       <c r="E37" t="n">
-        <v>3.0275</v>
+        <v>2.9604</v>
       </c>
       <c r="F37" t="n">
-        <v>3.0275</v>
+        <v>2.9604</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>3.0275</v>
+        <v>2.9604</v>
       </c>
       <c r="I37" t="n">
         <v>3.1131</v>
@@ -2152,25 +2152,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2.9782</v>
+        <v>2.9231</v>
       </c>
       <c r="C38" t="n">
-        <v>2.4015</v>
+        <v>2.3571</v>
       </c>
       <c r="D38" t="n">
-        <v>0.7818000000000001</v>
+        <v>0.7207</v>
       </c>
       <c r="E38" t="n">
-        <v>2.9782</v>
+        <v>2.9231</v>
       </c>
       <c r="F38" t="n">
-        <v>2.9782</v>
+        <v>2.9231</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>2.9782</v>
+        <v>2.9231</v>
       </c>
       <c r="I38" t="n">
         <v>3.0482</v>
@@ -2198,25 +2198,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2.9094</v>
+        <v>2.8663</v>
       </c>
       <c r="C39" t="n">
-        <v>2.346</v>
+        <v>2.3113</v>
       </c>
       <c r="D39" t="n">
-        <v>0.754</v>
+        <v>0.698</v>
       </c>
       <c r="E39" t="n">
-        <v>2.9094</v>
+        <v>2.8663</v>
       </c>
       <c r="F39" t="n">
-        <v>2.9094</v>
+        <v>2.8663</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>2.9094</v>
+        <v>2.8663</v>
       </c>
       <c r="I39" t="n">
         <v>2.964</v>
@@ -2244,25 +2244,25 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2.7654</v>
+        <v>2.7178</v>
       </c>
       <c r="C40" t="n">
-        <v>2.2299</v>
+        <v>2.1915</v>
       </c>
       <c r="D40" t="n">
-        <v>0.6958</v>
+        <v>0.6389</v>
       </c>
       <c r="E40" t="n">
-        <v>2.7654</v>
+        <v>2.7178</v>
       </c>
       <c r="F40" t="n">
-        <v>2.1448</v>
+        <v>2.0972</v>
       </c>
       <c r="G40" t="n">
         <v>0.6206</v>
       </c>
       <c r="H40" t="n">
-        <v>2.1448</v>
+        <v>2.0972</v>
       </c>
       <c r="I40" t="n">
         <v>2.2054</v>
@@ -2290,25 +2290,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2.7348</v>
+        <v>2.6741</v>
       </c>
       <c r="C41" t="n">
-        <v>2.2052</v>
+        <v>2.1563</v>
       </c>
       <c r="D41" t="n">
-        <v>0.6834</v>
+        <v>0.6215000000000001</v>
       </c>
       <c r="E41" t="n">
-        <v>2.7348</v>
+        <v>2.6741</v>
       </c>
       <c r="F41" t="n">
-        <v>2.7348</v>
+        <v>2.6741</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>2.7348</v>
+        <v>2.6741</v>
       </c>
       <c r="I41" t="n">
         <v>2.812</v>
@@ -2336,25 +2336,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2.68</v>
+        <v>2.6011</v>
       </c>
       <c r="C42" t="n">
-        <v>2.161</v>
+        <v>2.0974</v>
       </c>
       <c r="D42" t="n">
-        <v>0.6613</v>
+        <v>0.5924</v>
       </c>
       <c r="E42" t="n">
-        <v>2.68</v>
+        <v>2.6011</v>
       </c>
       <c r="F42" t="n">
-        <v>2.68</v>
+        <v>2.6011</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>2.68</v>
+        <v>2.6011</v>
       </c>
       <c r="I42" t="n">
         <v>2.7815</v>
@@ -2382,25 +2382,25 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2.6334</v>
+        <v>2.5463</v>
       </c>
       <c r="C43" t="n">
-        <v>2.1235</v>
+        <v>2.0532</v>
       </c>
       <c r="D43" t="n">
-        <v>0.6425</v>
+        <v>0.5705</v>
       </c>
       <c r="E43" t="n">
-        <v>2.6334</v>
+        <v>2.5463</v>
       </c>
       <c r="F43" t="n">
-        <v>2.6334</v>
+        <v>2.5463</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>2.6334</v>
+        <v>2.5463</v>
       </c>
       <c r="I43" t="n">
         <v>2.7458</v>
@@ -2428,25 +2428,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2.6187</v>
+        <v>2.541</v>
       </c>
       <c r="C44" t="n">
-        <v>2.1116</v>
+        <v>2.049</v>
       </c>
       <c r="D44" t="n">
-        <v>0.6365</v>
+        <v>0.5684</v>
       </c>
       <c r="E44" t="n">
-        <v>2.6187</v>
+        <v>2.541</v>
       </c>
       <c r="F44" t="n">
-        <v>3.5025</v>
+        <v>3.4248</v>
       </c>
       <c r="G44" t="n">
         <v>-0.8838</v>
       </c>
       <c r="H44" t="n">
-        <v>3.5025</v>
+        <v>3.4248</v>
       </c>
       <c r="I44" t="n">
         <v>3.6014</v>
@@ -2470,93 +2470,93 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>degster</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2.5921</v>
+        <v>2.5356</v>
       </c>
       <c r="C45" t="n">
-        <v>2.0902</v>
+        <v>2.0446</v>
       </c>
       <c r="D45" t="n">
-        <v>0.6258</v>
+        <v>0.5663</v>
       </c>
       <c r="E45" t="n">
-        <v>2.5921</v>
+        <v>2.5356</v>
       </c>
       <c r="F45" t="n">
-        <v>2.5921</v>
+        <v>2.5356</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>2.5921</v>
+        <v>2.5356</v>
       </c>
       <c r="I45" t="n">
-        <v>2.6653</v>
+        <v>2.6001</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>299</v>
+        <v>259</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>2.6653</v>
+        <v>2.6001</v>
       </c>
       <c r="N45" t="n">
-        <v>299</v>
+        <v>259</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>degster</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2.5642</v>
+        <v>2.5346</v>
       </c>
       <c r="C46" t="n">
-        <v>2.0677</v>
+        <v>2.0438</v>
       </c>
       <c r="D46" t="n">
-        <v>0.6145</v>
+        <v>0.5659</v>
       </c>
       <c r="E46" t="n">
-        <v>2.5642</v>
+        <v>2.5346</v>
       </c>
       <c r="F46" t="n">
-        <v>2.5642</v>
+        <v>2.5346</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>2.5642</v>
+        <v>2.5346</v>
       </c>
       <c r="I46" t="n">
-        <v>2.6001</v>
+        <v>2.6653</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>259</v>
+        <v>299</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>2.6001</v>
+        <v>2.6653</v>
       </c>
       <c r="N46" t="n">
-        <v>259</v>
+        <v>299</v>
       </c>
     </row>
     <row r="47">
@@ -2566,25 +2566,25 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2.5146</v>
+        <v>2.4405</v>
       </c>
       <c r="C47" t="n">
-        <v>2.0277</v>
+        <v>1.9679</v>
       </c>
       <c r="D47" t="n">
-        <v>0.5945</v>
+        <v>0.5284</v>
       </c>
       <c r="E47" t="n">
-        <v>2.5146</v>
+        <v>2.4405</v>
       </c>
       <c r="F47" t="n">
-        <v>2.5146</v>
+        <v>2.4405</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>2.5146</v>
+        <v>2.4405</v>
       </c>
       <c r="I47" t="n">
         <v>2.6097</v>
@@ -2612,25 +2612,25 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2.4877</v>
+        <v>2.4235</v>
       </c>
       <c r="C48" t="n">
-        <v>2.006</v>
+        <v>1.9542</v>
       </c>
       <c r="D48" t="n">
-        <v>0.5836</v>
+        <v>0.5216</v>
       </c>
       <c r="E48" t="n">
-        <v>2.4877</v>
+        <v>2.4235</v>
       </c>
       <c r="F48" t="n">
-        <v>2.4877</v>
+        <v>2.4235</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>2.4877</v>
+        <v>2.4235</v>
       </c>
       <c r="I48" t="n">
         <v>2.5699</v>
@@ -2654,93 +2654,93 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>zevy</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2.475</v>
+        <v>2.4076</v>
       </c>
       <c r="C49" t="n">
-        <v>1.9957</v>
+        <v>1.9414</v>
       </c>
       <c r="D49" t="n">
-        <v>0.5785</v>
+        <v>0.5153</v>
       </c>
       <c r="E49" t="n">
-        <v>2.475</v>
+        <v>2.4076</v>
       </c>
       <c r="F49" t="n">
-        <v>2.475</v>
+        <v>2.4076</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>2.475</v>
+        <v>2.4076</v>
       </c>
       <c r="I49" t="n">
-        <v>2.5806</v>
+        <v>2.5318</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>396</v>
+        <v>299</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>2.5806</v>
+        <v>2.5318</v>
       </c>
       <c r="N49" t="n">
-        <v>396</v>
+        <v>299</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>zevy</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2.4622</v>
+        <v>2.3931</v>
       </c>
       <c r="C50" t="n">
-        <v>1.9854</v>
+        <v>1.9297</v>
       </c>
       <c r="D50" t="n">
-        <v>0.5733</v>
+        <v>0.5095</v>
       </c>
       <c r="E50" t="n">
-        <v>2.4622</v>
+        <v>2.3931</v>
       </c>
       <c r="F50" t="n">
-        <v>2.4622</v>
+        <v>2.3931</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>2.4622</v>
+        <v>2.3931</v>
       </c>
       <c r="I50" t="n">
-        <v>2.5318</v>
+        <v>2.5806</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>299</v>
+        <v>396</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>2.5318</v>
+        <v>2.5806</v>
       </c>
       <c r="N50" t="n">
-        <v>299</v>
+        <v>396</v>
       </c>
     </row>
     <row r="51">
@@ -2750,25 +2750,25 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2.4033</v>
+        <v>2.3405</v>
       </c>
       <c r="C51" t="n">
-        <v>1.9379</v>
+        <v>1.8873</v>
       </c>
       <c r="D51" t="n">
-        <v>0.5495</v>
+        <v>0.4885</v>
       </c>
       <c r="E51" t="n">
-        <v>2.4033</v>
+        <v>2.3405</v>
       </c>
       <c r="F51" t="n">
-        <v>2.8305</v>
+        <v>2.7677</v>
       </c>
       <c r="G51" t="n">
         <v>-0.4272</v>
       </c>
       <c r="H51" t="n">
-        <v>2.8305</v>
+        <v>2.7677</v>
       </c>
       <c r="I51" t="n">
         <v>2.9105</v>
@@ -2792,93 +2792,93 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>nqz</t>
+          <t>imoRR</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2.3554</v>
+        <v>2.2919</v>
       </c>
       <c r="C52" t="n">
-        <v>1.8993</v>
+        <v>1.8481</v>
       </c>
       <c r="D52" t="n">
-        <v>0.5302</v>
+        <v>0.4692</v>
       </c>
       <c r="E52" t="n">
-        <v>2.3554</v>
+        <v>2.2919</v>
       </c>
       <c r="F52" t="n">
-        <v>2.3554</v>
+        <v>2.2919</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>2.3554</v>
+        <v>2.2919</v>
       </c>
       <c r="I52" t="n">
-        <v>2.4445</v>
+        <v>2.4101</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>462</v>
+        <v>329</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>2.4445</v>
+        <v>2.4101</v>
       </c>
       <c r="N52" t="n">
-        <v>462</v>
+        <v>329</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>imoRR</t>
+          <t>nqz</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2.3439</v>
+        <v>2.286</v>
       </c>
       <c r="C53" t="n">
-        <v>1.89</v>
+        <v>1.8433</v>
       </c>
       <c r="D53" t="n">
-        <v>0.5255</v>
+        <v>0.4668</v>
       </c>
       <c r="E53" t="n">
-        <v>2.3439</v>
+        <v>2.286</v>
       </c>
       <c r="F53" t="n">
-        <v>2.3439</v>
+        <v>2.286</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>2.3439</v>
+        <v>2.286</v>
       </c>
       <c r="I53" t="n">
-        <v>2.4101</v>
+        <v>2.4445</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>329</v>
+        <v>462</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>2.4101</v>
+        <v>2.4445</v>
       </c>
       <c r="N53" t="n">
-        <v>329</v>
+        <v>462</v>
       </c>
     </row>
     <row r="54">
@@ -2888,25 +2888,25 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2.3271</v>
+        <v>2.2501</v>
       </c>
       <c r="C54" t="n">
-        <v>1.8765</v>
+        <v>1.8144</v>
       </c>
       <c r="D54" t="n">
-        <v>0.5187</v>
+        <v>0.4525</v>
       </c>
       <c r="E54" t="n">
-        <v>2.3271</v>
+        <v>2.2501</v>
       </c>
       <c r="F54" t="n">
-        <v>2.3271</v>
+        <v>2.2501</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>2.3271</v>
+        <v>2.2501</v>
       </c>
       <c r="I54" t="n">
         <v>2.4264</v>
@@ -2934,25 +2934,25 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2.2325</v>
+        <v>2.183</v>
       </c>
       <c r="C55" t="n">
-        <v>1.8002</v>
+        <v>1.7603</v>
       </c>
       <c r="D55" t="n">
-        <v>0.4805</v>
+        <v>0.4258</v>
       </c>
       <c r="E55" t="n">
-        <v>2.2325</v>
+        <v>2.183</v>
       </c>
       <c r="F55" t="n">
-        <v>2.2325</v>
+        <v>2.183</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>2.2325</v>
+        <v>2.183</v>
       </c>
       <c r="I55" t="n">
         <v>2.2956</v>
@@ -2980,25 +2980,25 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2.1877</v>
+        <v>2.1392</v>
       </c>
       <c r="C56" t="n">
-        <v>1.7641</v>
+        <v>1.725</v>
       </c>
       <c r="D56" t="n">
-        <v>0.4624</v>
+        <v>0.4083</v>
       </c>
       <c r="E56" t="n">
-        <v>2.1877</v>
+        <v>2.1392</v>
       </c>
       <c r="F56" t="n">
-        <v>2.1877</v>
+        <v>2.1392</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>2.1877</v>
+        <v>2.1392</v>
       </c>
       <c r="I56" t="n">
         <v>2.2495</v>
@@ -3026,25 +3026,25 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2.0579</v>
+        <v>2.0047</v>
       </c>
       <c r="C57" t="n">
-        <v>1.6594</v>
+        <v>1.6165</v>
       </c>
       <c r="D57" t="n">
-        <v>0.41</v>
+        <v>0.3548</v>
       </c>
       <c r="E57" t="n">
-        <v>2.0579</v>
+        <v>2.0047</v>
       </c>
       <c r="F57" t="n">
-        <v>2.0579</v>
+        <v>2.0047</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>2.0579</v>
+        <v>2.0047</v>
       </c>
       <c r="I57" t="n">
         <v>2.1259</v>
@@ -3072,25 +3072,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2.0396</v>
+        <v>1.9721</v>
       </c>
       <c r="C58" t="n">
-        <v>1.6447</v>
+        <v>1.5902</v>
       </c>
       <c r="D58" t="n">
-        <v>0.4026</v>
+        <v>0.3418</v>
       </c>
       <c r="E58" t="n">
-        <v>2.0396</v>
+        <v>1.9721</v>
       </c>
       <c r="F58" t="n">
-        <v>2.0396</v>
+        <v>1.9721</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>2.0396</v>
+        <v>1.9721</v>
       </c>
       <c r="I58" t="n">
         <v>2.1266</v>
@@ -3118,25 +3118,25 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1.9924</v>
+        <v>1.9265</v>
       </c>
       <c r="C59" t="n">
-        <v>1.6066</v>
+        <v>1.5535</v>
       </c>
       <c r="D59" t="n">
-        <v>0.3835</v>
+        <v>0.3236</v>
       </c>
       <c r="E59" t="n">
-        <v>1.9924</v>
+        <v>1.9265</v>
       </c>
       <c r="F59" t="n">
-        <v>1.9924</v>
+        <v>1.9265</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>1.9924</v>
+        <v>1.9265</v>
       </c>
       <c r="I59" t="n">
         <v>2.0774</v>
@@ -3164,25 +3164,25 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1.9669</v>
+        <v>1.9233</v>
       </c>
       <c r="C60" t="n">
-        <v>1.586</v>
+        <v>1.5509</v>
       </c>
       <c r="D60" t="n">
-        <v>0.3732</v>
+        <v>0.3223</v>
       </c>
       <c r="E60" t="n">
-        <v>1.9669</v>
+        <v>1.9233</v>
       </c>
       <c r="F60" t="n">
-        <v>1.9669</v>
+        <v>1.9233</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>1.9669</v>
+        <v>1.9233</v>
       </c>
       <c r="I60" t="n">
         <v>2.0225</v>
@@ -3210,25 +3210,25 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1.8967</v>
+        <v>1.8602</v>
       </c>
       <c r="C61" t="n">
-        <v>1.5294</v>
+        <v>1.5</v>
       </c>
       <c r="D61" t="n">
-        <v>0.3449</v>
+        <v>0.2972</v>
       </c>
       <c r="E61" t="n">
-        <v>1.8967</v>
+        <v>1.8602</v>
       </c>
       <c r="F61" t="n">
-        <v>1.6457</v>
+        <v>1.6092</v>
       </c>
       <c r="G61" t="n">
         <v>0.251</v>
       </c>
       <c r="H61" t="n">
-        <v>1.6457</v>
+        <v>1.6092</v>
       </c>
       <c r="I61" t="n">
         <v>1.6922</v>
@@ -3256,25 +3256,25 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1.8373</v>
+        <v>1.7965</v>
       </c>
       <c r="C62" t="n">
-        <v>1.4815</v>
+        <v>1.4486</v>
       </c>
       <c r="D62" t="n">
-        <v>0.3209</v>
+        <v>0.2718</v>
       </c>
       <c r="E62" t="n">
-        <v>1.8373</v>
+        <v>1.7965</v>
       </c>
       <c r="F62" t="n">
-        <v>1.8373</v>
+        <v>1.7965</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>1.8373</v>
+        <v>1.7965</v>
       </c>
       <c r="I62" t="n">
         <v>1.8892</v>
@@ -3302,25 +3302,25 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1.7823</v>
+        <v>1.769</v>
       </c>
       <c r="C63" t="n">
-        <v>1.4372</v>
+        <v>1.4264</v>
       </c>
       <c r="D63" t="n">
-        <v>0.2986</v>
+        <v>0.2609</v>
       </c>
       <c r="E63" t="n">
-        <v>1.7823</v>
+        <v>1.769</v>
       </c>
       <c r="F63" t="n">
-        <v>1.7823</v>
+        <v>1.769</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>1.7823</v>
+        <v>1.769</v>
       </c>
       <c r="I63" t="n">
         <v>1.7989</v>
@@ -3348,25 +3348,25 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1.7224</v>
+        <v>1.6906</v>
       </c>
       <c r="C64" t="n">
-        <v>1.3889</v>
+        <v>1.3632</v>
       </c>
       <c r="D64" t="n">
-        <v>0.2744</v>
+        <v>0.2296</v>
       </c>
       <c r="E64" t="n">
-        <v>1.7224</v>
+        <v>1.6906</v>
       </c>
       <c r="F64" t="n">
-        <v>1.7224</v>
+        <v>1.6906</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>1.7224</v>
+        <v>1.6906</v>
       </c>
       <c r="I64" t="n">
         <v>1.7629</v>
@@ -3394,25 +3394,25 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1.7048</v>
+        <v>1.6858</v>
       </c>
       <c r="C65" t="n">
-        <v>1.3747</v>
+        <v>1.3594</v>
       </c>
       <c r="D65" t="n">
-        <v>0.2673</v>
+        <v>0.2277</v>
       </c>
       <c r="E65" t="n">
-        <v>1.7048</v>
+        <v>1.6858</v>
       </c>
       <c r="F65" t="n">
-        <v>1.7048</v>
+        <v>1.6858</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>1.7048</v>
+        <v>1.6858</v>
       </c>
       <c r="I65" t="n">
         <v>1.7288</v>
@@ -3440,25 +3440,25 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1.6268</v>
+        <v>1.5911</v>
       </c>
       <c r="C66" t="n">
-        <v>1.3118</v>
+        <v>1.283</v>
       </c>
       <c r="D66" t="n">
-        <v>0.2358</v>
+        <v>0.19</v>
       </c>
       <c r="E66" t="n">
-        <v>1.6268</v>
+        <v>1.5911</v>
       </c>
       <c r="F66" t="n">
-        <v>1.6106</v>
+        <v>1.5749</v>
       </c>
       <c r="G66" t="n">
         <v>0.0162</v>
       </c>
       <c r="H66" t="n">
-        <v>1.6106</v>
+        <v>1.5749</v>
       </c>
       <c r="I66" t="n">
         <v>1.6561</v>
@@ -3482,93 +3482,93 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Vexite</t>
+          <t>JOTA</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1.5021</v>
+        <v>1.4732</v>
       </c>
       <c r="C67" t="n">
-        <v>1.2112</v>
+        <v>1.1879</v>
       </c>
       <c r="D67" t="n">
-        <v>0.1855</v>
+        <v>0.143</v>
       </c>
       <c r="E67" t="n">
-        <v>1.5021</v>
+        <v>1.4732</v>
       </c>
       <c r="F67" t="n">
-        <v>1.5021</v>
+        <v>1.4732</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>1.5021</v>
+        <v>1.4732</v>
       </c>
       <c r="I67" t="n">
-        <v>1.5445</v>
+        <v>1.4981</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>363</v>
+        <v>241</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>1.5445</v>
+        <v>1.4981</v>
       </c>
       <c r="N67" t="n">
-        <v>363</v>
+        <v>241</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>JOTA</t>
+          <t>Vexite</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1.4843</v>
+        <v>1.4688</v>
       </c>
       <c r="C68" t="n">
-        <v>1.1969</v>
+        <v>1.1844</v>
       </c>
       <c r="D68" t="n">
-        <v>0.1783</v>
+        <v>0.1413</v>
       </c>
       <c r="E68" t="n">
-        <v>1.4843</v>
+        <v>1.4688</v>
       </c>
       <c r="F68" t="n">
-        <v>1.4843</v>
+        <v>1.4688</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>1.4843</v>
+        <v>1.4688</v>
       </c>
       <c r="I68" t="n">
-        <v>1.4981</v>
+        <v>1.5445</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>241</v>
+        <v>363</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>1.4981</v>
+        <v>1.5445</v>
       </c>
       <c r="N68" t="n">
-        <v>241</v>
+        <v>363</v>
       </c>
     </row>
     <row r="69">
@@ -3578,25 +3578,25 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1.4794</v>
+        <v>1.4629</v>
       </c>
       <c r="C69" t="n">
-        <v>1.1929</v>
+        <v>1.1796</v>
       </c>
       <c r="D69" t="n">
-        <v>0.1763</v>
+        <v>0.1389</v>
       </c>
       <c r="E69" t="n">
-        <v>1.4794</v>
+        <v>1.4629</v>
       </c>
       <c r="F69" t="n">
-        <v>1.4794</v>
+        <v>1.4629</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>1.4794</v>
+        <v>1.4629</v>
       </c>
       <c r="I69" t="n">
         <v>1.5002</v>
@@ -3620,93 +3620,93 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>chopper</t>
+          <t>nafany</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1.4668</v>
+        <v>1.4467</v>
       </c>
       <c r="C70" t="n">
-        <v>1.1828</v>
+        <v>1.1666</v>
       </c>
       <c r="D70" t="n">
-        <v>0.1712</v>
+        <v>0.1325</v>
       </c>
       <c r="E70" t="n">
-        <v>1.4668</v>
+        <v>1.4467</v>
       </c>
       <c r="F70" t="n">
-        <v>1.4668</v>
+        <v>0.244</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>1.2027</v>
       </c>
       <c r="H70" t="n">
-        <v>1.4668</v>
+        <v>0.244</v>
       </c>
       <c r="I70" t="n">
-        <v>1.5083</v>
+        <v>0.2566</v>
       </c>
       <c r="J70" t="n">
-        <v>0</v>
+        <v>1.2027</v>
       </c>
       <c r="K70" t="n">
-        <v>308</v>
+        <v>170</v>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>266</v>
       </c>
       <c r="M70" t="n">
-        <v>1.5083</v>
+        <v>1.4593</v>
       </c>
       <c r="N70" t="n">
-        <v>308</v>
+        <v>436</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>nafany</t>
+          <t>chopper</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1.4522</v>
+        <v>1.4343</v>
       </c>
       <c r="C71" t="n">
-        <v>1.171</v>
+        <v>1.1566</v>
       </c>
       <c r="D71" t="n">
-        <v>0.1653</v>
+        <v>0.1275</v>
       </c>
       <c r="E71" t="n">
-        <v>1.4522</v>
+        <v>1.4343</v>
       </c>
       <c r="F71" t="n">
-        <v>0.2495</v>
+        <v>1.4343</v>
       </c>
       <c r="G71" t="n">
-        <v>1.2027</v>
+        <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>0.2495</v>
+        <v>1.4343</v>
       </c>
       <c r="I71" t="n">
-        <v>0.2566</v>
+        <v>1.5083</v>
       </c>
       <c r="J71" t="n">
-        <v>1.2027</v>
+        <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>170</v>
+        <v>308</v>
       </c>
       <c r="L71" t="n">
-        <v>266</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>1.4593</v>
+        <v>1.5083</v>
       </c>
       <c r="N71" t="n">
-        <v>436</v>
+        <v>308</v>
       </c>
     </row>
     <row r="72">
@@ -3716,25 +3716,25 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1.3538</v>
+        <v>1.3238</v>
       </c>
       <c r="C72" t="n">
-        <v>1.0916</v>
+        <v>1.0675</v>
       </c>
       <c r="D72" t="n">
-        <v>0.1255</v>
+        <v>0.0835</v>
       </c>
       <c r="E72" t="n">
-        <v>1.3538</v>
+        <v>1.3238</v>
       </c>
       <c r="F72" t="n">
-        <v>1.3538</v>
+        <v>1.3238</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>1.3538</v>
+        <v>1.3238</v>
       </c>
       <c r="I72" t="n">
         <v>1.3921</v>
@@ -3758,93 +3758,93 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>shalfey</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1.332</v>
+        <v>1.2892</v>
       </c>
       <c r="C73" t="n">
-        <v>1.0741</v>
+        <v>1.0396</v>
       </c>
       <c r="D73" t="n">
-        <v>0.1167</v>
+        <v>0.0697</v>
       </c>
       <c r="E73" t="n">
-        <v>1.332</v>
+        <v>1.2892</v>
       </c>
       <c r="F73" t="n">
-        <v>2.0707</v>
+        <v>1.2892</v>
       </c>
       <c r="G73" t="n">
-        <v>-0.7387</v>
+        <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>2.0707</v>
+        <v>1.2892</v>
       </c>
       <c r="I73" t="n">
-        <v>2.1292</v>
+        <v>1.3786</v>
       </c>
       <c r="J73" t="n">
-        <v>-0.7387</v>
+        <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>199</v>
+        <v>400</v>
       </c>
       <c r="L73" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>1.3905</v>
+        <v>1.3786</v>
       </c>
       <c r="N73" t="n">
-        <v>280</v>
+        <v>400</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>shalfey</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1.3284</v>
+        <v>1.2861</v>
       </c>
       <c r="C74" t="n">
-        <v>1.0712</v>
+        <v>1.0371</v>
       </c>
       <c r="D74" t="n">
-        <v>0.1153</v>
+        <v>0.06850000000000001</v>
       </c>
       <c r="E74" t="n">
-        <v>1.3284</v>
+        <v>1.2861</v>
       </c>
       <c r="F74" t="n">
-        <v>1.3284</v>
+        <v>2.0248</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>-0.7387</v>
       </c>
       <c r="H74" t="n">
-        <v>1.3284</v>
+        <v>2.0248</v>
       </c>
       <c r="I74" t="n">
-        <v>1.3786</v>
+        <v>2.1292</v>
       </c>
       <c r="J74" t="n">
-        <v>0</v>
+        <v>-0.7387</v>
       </c>
       <c r="K74" t="n">
-        <v>400</v>
+        <v>199</v>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="M74" t="n">
-        <v>1.3786</v>
+        <v>1.3905</v>
       </c>
       <c r="N74" t="n">
-        <v>400</v>
+        <v>280</v>
       </c>
     </row>
     <row r="75">
@@ -3854,25 +3854,25 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1.2938</v>
+        <v>1.251</v>
       </c>
       <c r="C75" t="n">
-        <v>1.0433</v>
+        <v>1.0088</v>
       </c>
       <c r="D75" t="n">
-        <v>0.1013</v>
+        <v>0.0545</v>
       </c>
       <c r="E75" t="n">
-        <v>1.2938</v>
+        <v>1.251</v>
       </c>
       <c r="F75" t="n">
-        <v>1.2938</v>
+        <v>1.251</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>1.2938</v>
+        <v>1.251</v>
       </c>
       <c r="I75" t="n">
         <v>1.349</v>
@@ -3900,25 +3900,25 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1.1753</v>
+        <v>1.1362</v>
       </c>
       <c r="C76" t="n">
-        <v>0.9477</v>
+        <v>0.9162</v>
       </c>
       <c r="D76" t="n">
-        <v>0.0534</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="E76" t="n">
-        <v>1.1753</v>
+        <v>1.1362</v>
       </c>
       <c r="F76" t="n">
-        <v>1.7658</v>
+        <v>1.7267</v>
       </c>
       <c r="G76" t="n">
         <v>-0.5905</v>
       </c>
       <c r="H76" t="n">
-        <v>1.7658</v>
+        <v>1.7267</v>
       </c>
       <c r="I76" t="n">
         <v>1.8157</v>
@@ -3946,25 +3946,25 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1.1564</v>
+        <v>1.1224</v>
       </c>
       <c r="C77" t="n">
-        <v>0.9325</v>
+        <v>0.9051</v>
       </c>
       <c r="D77" t="n">
-        <v>0.0458</v>
+        <v>0.0033</v>
       </c>
       <c r="E77" t="n">
-        <v>1.1564</v>
+        <v>1.1224</v>
       </c>
       <c r="F77" t="n">
-        <v>1.1564</v>
+        <v>1.1224</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>1.1564</v>
+        <v>1.1224</v>
       </c>
       <c r="I77" t="n">
         <v>1.2002</v>
@@ -3992,25 +3992,25 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>1.0993</v>
+        <v>1.0911</v>
       </c>
       <c r="C78" t="n">
-        <v>0.8864</v>
+        <v>0.8798</v>
       </c>
       <c r="D78" t="n">
-        <v>0.0227</v>
+        <v>-0.0092</v>
       </c>
       <c r="E78" t="n">
-        <v>1.0993</v>
+        <v>1.0911</v>
       </c>
       <c r="F78" t="n">
-        <v>1.0993</v>
+        <v>1.0911</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>1.0993</v>
+        <v>1.0911</v>
       </c>
       <c r="I78" t="n">
         <v>1.1095</v>
@@ -4038,25 +4038,25 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>1.0973</v>
+        <v>1.0514</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8848</v>
+        <v>0.8478</v>
       </c>
       <c r="D79" t="n">
-        <v>0.0219</v>
+        <v>-0.025</v>
       </c>
       <c r="E79" t="n">
-        <v>1.0973</v>
+        <v>1.0514</v>
       </c>
       <c r="F79" t="n">
-        <v>2.071</v>
+        <v>2.0251</v>
       </c>
       <c r="G79" t="n">
         <v>-0.9737</v>
       </c>
       <c r="H79" t="n">
-        <v>2.071</v>
+        <v>2.0251</v>
       </c>
       <c r="I79" t="n">
         <v>2.1295</v>
@@ -4084,25 +4084,25 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>1.0523</v>
+        <v>1.0405</v>
       </c>
       <c r="C80" t="n">
-        <v>0.8485</v>
+        <v>0.839</v>
       </c>
       <c r="D80" t="n">
-        <v>0.0037</v>
+        <v>-0.0294</v>
       </c>
       <c r="E80" t="n">
-        <v>1.0523</v>
+        <v>1.0405</v>
       </c>
       <c r="F80" t="n">
-        <v>1.0523</v>
+        <v>1.0405</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>1.0523</v>
+        <v>1.0405</v>
       </c>
       <c r="I80" t="n">
         <v>1.067</v>
@@ -4130,25 +4130,25 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1.0405</v>
+        <v>1.0174</v>
       </c>
       <c r="C81" t="n">
-        <v>0.839</v>
+        <v>0.8204</v>
       </c>
       <c r="D81" t="n">
-        <v>-0.001</v>
+        <v>-0.0386</v>
       </c>
       <c r="E81" t="n">
-        <v>1.0405</v>
+        <v>1.0174</v>
       </c>
       <c r="F81" t="n">
-        <v>1.0405</v>
+        <v>1.0174</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>1.0405</v>
+        <v>1.0174</v>
       </c>
       <c r="I81" t="n">
         <v>1.0699</v>
@@ -4176,25 +4176,25 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1.0106</v>
+        <v>0.9984</v>
       </c>
       <c r="C82" t="n">
-        <v>0.8149</v>
+        <v>0.8051</v>
       </c>
       <c r="D82" t="n">
-        <v>-0.0131</v>
+        <v>-0.0461</v>
       </c>
       <c r="E82" t="n">
-        <v>1.0106</v>
+        <v>0.9984</v>
       </c>
       <c r="F82" t="n">
-        <v>0.5517</v>
+        <v>0.5395</v>
       </c>
       <c r="G82" t="n">
         <v>0.4589</v>
       </c>
       <c r="H82" t="n">
-        <v>0.5517</v>
+        <v>0.5395</v>
       </c>
       <c r="I82" t="n">
         <v>0.5673</v>
@@ -4222,25 +4222,25 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.9902</v>
+        <v>0.9683</v>
       </c>
       <c r="C83" t="n">
-        <v>0.7985</v>
+        <v>0.7808</v>
       </c>
       <c r="D83" t="n">
-        <v>-0.0213</v>
+        <v>-0.0581</v>
       </c>
       <c r="E83" t="n">
-        <v>0.9902</v>
+        <v>0.9683</v>
       </c>
       <c r="F83" t="n">
-        <v>0.9902</v>
+        <v>0.9683</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>0.9902</v>
+        <v>0.9683</v>
       </c>
       <c r="I83" t="n">
         <v>1.0182</v>
@@ -4268,25 +4268,25 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.8193</v>
+        <v>0.8018999999999999</v>
       </c>
       <c r="C84" t="n">
-        <v>0.6607</v>
+        <v>0.6466</v>
       </c>
       <c r="D84" t="n">
-        <v>-0.09039999999999999</v>
+        <v>-0.1244</v>
       </c>
       <c r="E84" t="n">
-        <v>0.8193</v>
+        <v>0.8018999999999999</v>
       </c>
       <c r="F84" t="n">
-        <v>0.7852</v>
+        <v>0.7678</v>
       </c>
       <c r="G84" t="n">
         <v>0.0341</v>
       </c>
       <c r="H84" t="n">
-        <v>0.7852</v>
+        <v>0.7678</v>
       </c>
       <c r="I84" t="n">
         <v>0.8074</v>
@@ -4310,93 +4310,93 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>buster</t>
+          <t>Tuurtle</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.7036</v>
+        <v>0.6877</v>
       </c>
       <c r="C85" t="n">
-        <v>0.5674</v>
+        <v>0.5545</v>
       </c>
       <c r="D85" t="n">
-        <v>-0.1371</v>
+        <v>-0.1699</v>
       </c>
       <c r="E85" t="n">
-        <v>0.7036</v>
+        <v>0.6877</v>
       </c>
       <c r="F85" t="n">
-        <v>1.2618</v>
+        <v>0.6877</v>
       </c>
       <c r="G85" t="n">
-        <v>-0.5582</v>
+        <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>1.2618</v>
+        <v>0.6877</v>
       </c>
       <c r="I85" t="n">
-        <v>1.2975</v>
+        <v>0.6993</v>
       </c>
       <c r="J85" t="n">
-        <v>-0.5582</v>
+        <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>170</v>
+        <v>214</v>
       </c>
       <c r="L85" t="n">
-        <v>266</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>0.7393000000000001</v>
+        <v>0.6993</v>
       </c>
       <c r="N85" t="n">
-        <v>436</v>
+        <v>214</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Tuurtle</t>
+          <t>buster</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.6928</v>
+        <v>0.6757</v>
       </c>
       <c r="C86" t="n">
-        <v>0.5586</v>
+        <v>0.5449000000000001</v>
       </c>
       <c r="D86" t="n">
-        <v>-0.1415</v>
+        <v>-0.1747</v>
       </c>
       <c r="E86" t="n">
-        <v>0.6928</v>
+        <v>0.6757</v>
       </c>
       <c r="F86" t="n">
-        <v>0.6928</v>
+        <v>1.2339</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>-0.5582</v>
       </c>
       <c r="H86" t="n">
-        <v>0.6928</v>
+        <v>1.2339</v>
       </c>
       <c r="I86" t="n">
-        <v>0.6993</v>
+        <v>1.2975</v>
       </c>
       <c r="J86" t="n">
-        <v>0</v>
+        <v>-0.5582</v>
       </c>
       <c r="K86" t="n">
-        <v>214</v>
+        <v>170</v>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>266</v>
       </c>
       <c r="M86" t="n">
-        <v>0.6993</v>
+        <v>0.7393000000000001</v>
       </c>
       <c r="N86" t="n">
-        <v>214</v>
+        <v>436</v>
       </c>
     </row>
     <row r="87">
@@ -4406,25 +4406,25 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.6152</v>
+        <v>0.5971</v>
       </c>
       <c r="C87" t="n">
-        <v>0.4961</v>
+        <v>0.4815</v>
       </c>
       <c r="D87" t="n">
-        <v>-0.1728</v>
+        <v>-0.206</v>
       </c>
       <c r="E87" t="n">
-        <v>0.6152</v>
+        <v>0.5971</v>
       </c>
       <c r="F87" t="n">
-        <v>0.6152</v>
+        <v>0.5971</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>0.6152</v>
+        <v>0.5971</v>
       </c>
       <c r="I87" t="n">
         <v>0.6385</v>
@@ -4452,25 +4452,25 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5711000000000001</v>
+        <v>0.5605</v>
       </c>
       <c r="C88" t="n">
-        <v>0.4605</v>
+        <v>0.452</v>
       </c>
       <c r="D88" t="n">
-        <v>-0.1907</v>
+        <v>-0.2206</v>
       </c>
       <c r="E88" t="n">
-        <v>0.5711000000000001</v>
+        <v>0.5605</v>
       </c>
       <c r="F88" t="n">
-        <v>0.5711000000000001</v>
+        <v>0.5605</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>0.5711000000000001</v>
+        <v>0.5605</v>
       </c>
       <c r="I88" t="n">
         <v>0.5845</v>
@@ -4498,25 +4498,25 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5514</v>
+        <v>0.5311</v>
       </c>
       <c r="C89" t="n">
-        <v>0.4446</v>
+        <v>0.4283</v>
       </c>
       <c r="D89" t="n">
-        <v>-0.1986</v>
+        <v>-0.2323</v>
       </c>
       <c r="E89" t="n">
-        <v>0.5514</v>
+        <v>0.5311</v>
       </c>
       <c r="F89" t="n">
-        <v>0.9113</v>
+        <v>0.891</v>
       </c>
       <c r="G89" t="n">
         <v>-0.3599</v>
       </c>
       <c r="H89" t="n">
-        <v>0.9113</v>
+        <v>0.891</v>
       </c>
       <c r="I89" t="n">
         <v>0.9370000000000001</v>
@@ -4544,25 +4544,25 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5272</v>
+        <v>0.5155</v>
       </c>
       <c r="C90" t="n">
-        <v>0.4251</v>
+        <v>0.4157</v>
       </c>
       <c r="D90" t="n">
-        <v>-0.2084</v>
+        <v>-0.2385</v>
       </c>
       <c r="E90" t="n">
-        <v>0.5272</v>
+        <v>0.5155</v>
       </c>
       <c r="F90" t="n">
-        <v>0.5272</v>
+        <v>0.5155</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>0.5272</v>
+        <v>0.5155</v>
       </c>
       <c r="I90" t="n">
         <v>0.5421</v>
@@ -4590,25 +4590,25 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.502</v>
+        <v>0.4785</v>
       </c>
       <c r="C91" t="n">
-        <v>0.4048</v>
+        <v>0.3858</v>
       </c>
       <c r="D91" t="n">
-        <v>-0.2186</v>
+        <v>-0.2533</v>
       </c>
       <c r="E91" t="n">
-        <v>0.502</v>
+        <v>0.4785</v>
       </c>
       <c r="F91" t="n">
-        <v>1.0614</v>
+        <v>1.0379</v>
       </c>
       <c r="G91" t="n">
         <v>-0.5594</v>
       </c>
       <c r="H91" t="n">
-        <v>1.0614</v>
+        <v>1.0379</v>
       </c>
       <c r="I91" t="n">
         <v>1.0914</v>
@@ -4636,25 +4636,25 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.4456</v>
+        <v>0.4407</v>
       </c>
       <c r="C92" t="n">
-        <v>0.3593</v>
+        <v>0.3554</v>
       </c>
       <c r="D92" t="n">
-        <v>-0.2413</v>
+        <v>-0.2683</v>
       </c>
       <c r="E92" t="n">
-        <v>0.4456</v>
+        <v>0.4407</v>
       </c>
       <c r="F92" t="n">
-        <v>0.4456</v>
+        <v>0.4407</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>0.4456</v>
+        <v>0.4407</v>
       </c>
       <c r="I92" t="n">
         <v>0.4519</v>
@@ -4682,25 +4682,25 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.4298</v>
+        <v>0.425</v>
       </c>
       <c r="C93" t="n">
-        <v>0.3466</v>
+        <v>0.3427</v>
       </c>
       <c r="D93" t="n">
-        <v>-0.2477</v>
+        <v>-0.2746</v>
       </c>
       <c r="E93" t="n">
-        <v>0.4298</v>
+        <v>0.425</v>
       </c>
       <c r="F93" t="n">
-        <v>0.4298</v>
+        <v>0.425</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>0.4298</v>
+        <v>0.425</v>
       </c>
       <c r="I93" t="n">
         <v>0.4358</v>
@@ -4728,25 +4728,25 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.4125</v>
+        <v>0.4079</v>
       </c>
       <c r="C94" t="n">
-        <v>0.3326</v>
+        <v>0.3289</v>
       </c>
       <c r="D94" t="n">
-        <v>-0.2547</v>
+        <v>-0.2814</v>
       </c>
       <c r="E94" t="n">
-        <v>0.4125</v>
+        <v>0.4079</v>
       </c>
       <c r="F94" t="n">
-        <v>0.4125</v>
+        <v>0.4079</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>0.4125</v>
+        <v>0.4079</v>
       </c>
       <c r="I94" t="n">
         <v>0.4183</v>
@@ -4774,25 +4774,25 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.4074</v>
+        <v>0.4044</v>
       </c>
       <c r="C95" t="n">
-        <v>0.3285</v>
+        <v>0.3261</v>
       </c>
       <c r="D95" t="n">
-        <v>-0.2568</v>
+        <v>-0.2828</v>
       </c>
       <c r="E95" t="n">
-        <v>0.4074</v>
+        <v>0.4044</v>
       </c>
       <c r="F95" t="n">
-        <v>0.4074</v>
+        <v>0.4044</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>0.4074</v>
+        <v>0.4044</v>
       </c>
       <c r="I95" t="n">
         <v>0.4112</v>
@@ -4820,25 +4820,25 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.3903</v>
+        <v>0.3888</v>
       </c>
       <c r="C96" t="n">
-        <v>0.3147</v>
+        <v>0.3135</v>
       </c>
       <c r="D96" t="n">
-        <v>-0.2637</v>
+        <v>-0.289</v>
       </c>
       <c r="E96" t="n">
-        <v>0.3903</v>
+        <v>0.3888</v>
       </c>
       <c r="F96" t="n">
-        <v>0.3903</v>
+        <v>0.3888</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>0.3903</v>
+        <v>0.3888</v>
       </c>
       <c r="I96" t="n">
         <v>0.3921</v>
@@ -4866,25 +4866,25 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.3605</v>
+        <v>0.3525</v>
       </c>
       <c r="C97" t="n">
-        <v>0.2907</v>
+        <v>0.2842</v>
       </c>
       <c r="D97" t="n">
-        <v>-0.2757</v>
+        <v>-0.3035</v>
       </c>
       <c r="E97" t="n">
-        <v>0.3605</v>
+        <v>0.3525</v>
       </c>
       <c r="F97" t="n">
-        <v>0.3605</v>
+        <v>0.3525</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>0.3605</v>
+        <v>0.3525</v>
       </c>
       <c r="I97" t="n">
         <v>0.3707</v>
@@ -4912,25 +4912,25 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.2705</v>
+        <v>0.2685</v>
       </c>
       <c r="C98" t="n">
-        <v>0.2181</v>
+        <v>0.2165</v>
       </c>
       <c r="D98" t="n">
-        <v>-0.3121</v>
+        <v>-0.3369</v>
       </c>
       <c r="E98" t="n">
-        <v>0.2705</v>
+        <v>0.2685</v>
       </c>
       <c r="F98" t="n">
-        <v>0.2705</v>
+        <v>0.2685</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>0.2705</v>
+        <v>0.2685</v>
       </c>
       <c r="I98" t="n">
         <v>0.273</v>
@@ -4958,25 +4958,25 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.2575</v>
+        <v>0.2556</v>
       </c>
       <c r="C99" t="n">
-        <v>0.2076</v>
+        <v>0.2061</v>
       </c>
       <c r="D99" t="n">
-        <v>-0.3173</v>
+        <v>-0.3421</v>
       </c>
       <c r="E99" t="n">
-        <v>0.2575</v>
+        <v>0.2556</v>
       </c>
       <c r="F99" t="n">
-        <v>0.2575</v>
+        <v>0.2556</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
       </c>
       <c r="H99" t="n">
-        <v>0.2575</v>
+        <v>0.2556</v>
       </c>
       <c r="I99" t="n">
         <v>0.2599</v>
@@ -5004,25 +5004,25 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.2488</v>
+        <v>0.2406</v>
       </c>
       <c r="C100" t="n">
-        <v>0.2006</v>
+        <v>0.194</v>
       </c>
       <c r="D100" t="n">
-        <v>-0.3209</v>
+        <v>-0.3481</v>
       </c>
       <c r="E100" t="n">
-        <v>0.2488</v>
+        <v>0.2406</v>
       </c>
       <c r="F100" t="n">
-        <v>0.2488</v>
+        <v>0.2406</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
       </c>
       <c r="H100" t="n">
-        <v>0.2488</v>
+        <v>0.2406</v>
       </c>
       <c r="I100" t="n">
         <v>0.2594</v>
@@ -5050,25 +5050,25 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.2308</v>
+        <v>0.2291</v>
       </c>
       <c r="C101" t="n">
-        <v>0.1861</v>
+        <v>0.1847</v>
       </c>
       <c r="D101" t="n">
-        <v>-0.3281</v>
+        <v>-0.3526</v>
       </c>
       <c r="E101" t="n">
-        <v>0.2308</v>
+        <v>0.2291</v>
       </c>
       <c r="F101" t="n">
-        <v>0.2308</v>
+        <v>0.2291</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
       </c>
       <c r="H101" t="n">
-        <v>0.2308</v>
+        <v>0.2291</v>
       </c>
       <c r="I101" t="n">
         <v>0.233</v>
@@ -5096,25 +5096,25 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.1835</v>
+        <v>0.163</v>
       </c>
       <c r="C102" t="n">
-        <v>0.148</v>
+        <v>0.1314</v>
       </c>
       <c r="D102" t="n">
-        <v>-0.3472</v>
+        <v>-0.379</v>
       </c>
       <c r="E102" t="n">
-        <v>0.1835</v>
+        <v>0.163</v>
       </c>
       <c r="F102" t="n">
-        <v>0.9262</v>
+        <v>0.9056999999999999</v>
       </c>
       <c r="G102" t="n">
         <v>-0.7427</v>
       </c>
       <c r="H102" t="n">
-        <v>0.9262</v>
+        <v>0.9056999999999999</v>
       </c>
       <c r="I102" t="n">
         <v>0.9524</v>
@@ -5142,25 +5142,25 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.12</v>
+        <v>0.1191</v>
       </c>
       <c r="C103" t="n">
-        <v>0.0968</v>
+        <v>0.096</v>
       </c>
       <c r="D103" t="n">
-        <v>-0.3729</v>
+        <v>-0.3965</v>
       </c>
       <c r="E103" t="n">
-        <v>0.12</v>
+        <v>0.1191</v>
       </c>
       <c r="F103" t="n">
-        <v>0.12</v>
+        <v>0.1191</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
       </c>
       <c r="H103" t="n">
-        <v>0.12</v>
+        <v>0.1191</v>
       </c>
       <c r="I103" t="n">
         <v>0.1211</v>
@@ -5188,25 +5188,25 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.0998</v>
+        <v>0.1027</v>
       </c>
       <c r="C104" t="n">
-        <v>0.0805</v>
+        <v>0.0828</v>
       </c>
       <c r="D104" t="n">
-        <v>-0.381</v>
+        <v>-0.403</v>
       </c>
       <c r="E104" t="n">
-        <v>0.0998</v>
+        <v>0.1027</v>
       </c>
       <c r="F104" t="n">
-        <v>-0.1313</v>
+        <v>-0.1284</v>
       </c>
       <c r="G104" t="n">
         <v>0.2311</v>
       </c>
       <c r="H104" t="n">
-        <v>-0.1313</v>
+        <v>-0.1284</v>
       </c>
       <c r="I104" t="n">
         <v>-0.135</v>
@@ -5234,25 +5234,25 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.09</v>
+        <v>0.0893</v>
       </c>
       <c r="C105" t="n">
-        <v>0.0726</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="D105" t="n">
-        <v>-0.385</v>
+        <v>-0.4083</v>
       </c>
       <c r="E105" t="n">
-        <v>0.09</v>
+        <v>0.0893</v>
       </c>
       <c r="F105" t="n">
-        <v>0.09</v>
+        <v>0.0893</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
       </c>
       <c r="H105" t="n">
-        <v>0.09</v>
+        <v>0.0893</v>
       </c>
       <c r="I105" t="n">
         <v>0.09080000000000001</v>
@@ -5280,25 +5280,25 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>-0.0161</v>
+        <v>-0.016</v>
       </c>
       <c r="C106" t="n">
-        <v>-0.013</v>
+        <v>-0.0129</v>
       </c>
       <c r="D106" t="n">
-        <v>-0.4279</v>
+        <v>-0.4503</v>
       </c>
       <c r="E106" t="n">
-        <v>-0.0161</v>
+        <v>-0.016</v>
       </c>
       <c r="F106" t="n">
-        <v>-0.0161</v>
+        <v>-0.016</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
       </c>
       <c r="H106" t="n">
-        <v>-0.0161</v>
+        <v>-0.016</v>
       </c>
       <c r="I106" t="n">
         <v>-0.0163</v>
@@ -5326,25 +5326,25 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>-0.09760000000000001</v>
+        <v>-0.0969</v>
       </c>
       <c r="C107" t="n">
-        <v>-0.07870000000000001</v>
+        <v>-0.0781</v>
       </c>
       <c r="D107" t="n">
-        <v>-0.4608</v>
+        <v>-0.4825</v>
       </c>
       <c r="E107" t="n">
-        <v>-0.09760000000000001</v>
+        <v>-0.0969</v>
       </c>
       <c r="F107" t="n">
-        <v>-0.09760000000000001</v>
+        <v>-0.0969</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
       </c>
       <c r="H107" t="n">
-        <v>-0.09760000000000001</v>
+        <v>-0.0969</v>
       </c>
       <c r="I107" t="n">
         <v>-0.0985</v>
@@ -5372,25 +5372,25 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>-0.1123</v>
+        <v>-0.1114</v>
       </c>
       <c r="C108" t="n">
-        <v>-0.0906</v>
+        <v>-0.0898</v>
       </c>
       <c r="D108" t="n">
-        <v>-0.4667</v>
+        <v>-0.4883</v>
       </c>
       <c r="E108" t="n">
-        <v>-0.1123</v>
+        <v>-0.1114</v>
       </c>
       <c r="F108" t="n">
-        <v>-0.1123</v>
+        <v>-0.1114</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
       </c>
       <c r="H108" t="n">
-        <v>-0.1123</v>
+        <v>-0.1114</v>
       </c>
       <c r="I108" t="n">
         <v>-0.1133</v>
@@ -5424,7 +5424,7 @@
         <v>-0.09180000000000001</v>
       </c>
       <c r="D109" t="n">
-        <v>-0.4674</v>
+        <v>-0.4893</v>
       </c>
       <c r="E109" t="n">
         <v>-0.1139</v>
@@ -5464,25 +5464,25 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>-0.141</v>
+        <v>-0.1405</v>
       </c>
       <c r="C110" t="n">
-        <v>-0.1137</v>
+        <v>-0.1133</v>
       </c>
       <c r="D110" t="n">
-        <v>-0.4783</v>
+        <v>-0.4999</v>
       </c>
       <c r="E110" t="n">
-        <v>-0.141</v>
+        <v>-0.1405</v>
       </c>
       <c r="F110" t="n">
-        <v>-0.141</v>
+        <v>-0.1405</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
       </c>
       <c r="H110" t="n">
-        <v>-0.141</v>
+        <v>-0.1405</v>
       </c>
       <c r="I110" t="n">
         <v>-0.1417</v>
@@ -5510,25 +5510,25 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>-0.1462</v>
+        <v>-0.1446</v>
       </c>
       <c r="C111" t="n">
-        <v>-0.1179</v>
+        <v>-0.1166</v>
       </c>
       <c r="D111" t="n">
-        <v>-0.4804</v>
+        <v>-0.5014999999999999</v>
       </c>
       <c r="E111" t="n">
-        <v>-0.1462</v>
+        <v>-0.1446</v>
       </c>
       <c r="F111" t="n">
-        <v>-0.1462</v>
+        <v>-0.1446</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
       </c>
       <c r="H111" t="n">
-        <v>-0.1462</v>
+        <v>-0.1446</v>
       </c>
       <c r="I111" t="n">
         <v>-0.1483</v>
@@ -5556,25 +5556,25 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>-0.1527</v>
+        <v>-0.1499</v>
       </c>
       <c r="C112" t="n">
-        <v>-0.1231</v>
+        <v>-0.1209</v>
       </c>
       <c r="D112" t="n">
-        <v>-0.483</v>
+        <v>-0.5036</v>
       </c>
       <c r="E112" t="n">
-        <v>-0.1527</v>
+        <v>-0.1499</v>
       </c>
       <c r="F112" t="n">
-        <v>-0.1527</v>
+        <v>-0.1499</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
       </c>
       <c r="H112" t="n">
-        <v>-0.1527</v>
+        <v>-0.1499</v>
       </c>
       <c r="I112" t="n">
         <v>-0.1563</v>
@@ -5602,25 +5602,25 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>-0.1785</v>
+        <v>-0.1758</v>
       </c>
       <c r="C113" t="n">
-        <v>-0.1439</v>
+        <v>-0.1418</v>
       </c>
       <c r="D113" t="n">
-        <v>-0.4935</v>
+        <v>-0.5139</v>
       </c>
       <c r="E113" t="n">
-        <v>-0.1785</v>
+        <v>-0.1758</v>
       </c>
       <c r="F113" t="n">
-        <v>-0.1785</v>
+        <v>-0.1758</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
       </c>
       <c r="H113" t="n">
-        <v>-0.1785</v>
+        <v>-0.1758</v>
       </c>
       <c r="I113" t="n">
         <v>-0.1818</v>
@@ -5648,25 +5648,25 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>-0.2163</v>
+        <v>-0.2139</v>
       </c>
       <c r="C114" t="n">
-        <v>-0.1744</v>
+        <v>-0.1725</v>
       </c>
       <c r="D114" t="n">
-        <v>-0.5087</v>
+        <v>-0.5291</v>
       </c>
       <c r="E114" t="n">
-        <v>-0.2163</v>
+        <v>-0.2139</v>
       </c>
       <c r="F114" t="n">
-        <v>-0.2163</v>
+        <v>-0.2139</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
       </c>
       <c r="H114" t="n">
-        <v>-0.2163</v>
+        <v>-0.2139</v>
       </c>
       <c r="I114" t="n">
         <v>-0.2193</v>
@@ -5694,25 +5694,25 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>-0.2637</v>
+        <v>-0.2627</v>
       </c>
       <c r="C115" t="n">
-        <v>-0.2126</v>
+        <v>-0.2118</v>
       </c>
       <c r="D115" t="n">
-        <v>-0.5279</v>
+        <v>-0.5486</v>
       </c>
       <c r="E115" t="n">
-        <v>-0.2637</v>
+        <v>-0.2627</v>
       </c>
       <c r="F115" t="n">
-        <v>-0.2637</v>
+        <v>-0.2627</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
       </c>
       <c r="H115" t="n">
-        <v>-0.2637</v>
+        <v>-0.2627</v>
       </c>
       <c r="I115" t="n">
         <v>-0.2649</v>
@@ -5740,25 +5740,25 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>-0.3427</v>
+        <v>-0.3414</v>
       </c>
       <c r="C116" t="n">
-        <v>-0.2763</v>
+        <v>-0.2753</v>
       </c>
       <c r="D116" t="n">
-        <v>-0.5598</v>
+        <v>-0.5799</v>
       </c>
       <c r="E116" t="n">
-        <v>-0.3427</v>
+        <v>-0.3414</v>
       </c>
       <c r="F116" t="n">
-        <v>-0.3427</v>
+        <v>-0.3414</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
       </c>
       <c r="H116" t="n">
-        <v>-0.3427</v>
+        <v>-0.3414</v>
       </c>
       <c r="I116" t="n">
         <v>-0.3443</v>
@@ -5786,25 +5786,25 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>-0.3694</v>
+        <v>-0.3626</v>
       </c>
       <c r="C117" t="n">
-        <v>-0.2979</v>
+        <v>-0.2924</v>
       </c>
       <c r="D117" t="n">
-        <v>-0.5706</v>
+        <v>-0.5884</v>
       </c>
       <c r="E117" t="n">
-        <v>-0.3694</v>
+        <v>-0.3626</v>
       </c>
       <c r="F117" t="n">
-        <v>-0.3694</v>
+        <v>-0.3626</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
       </c>
       <c r="H117" t="n">
-        <v>-0.3694</v>
+        <v>-0.3626</v>
       </c>
       <c r="I117" t="n">
         <v>-0.3781</v>
@@ -5832,25 +5832,25 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>-0.4683</v>
+        <v>-0.4631</v>
       </c>
       <c r="C118" t="n">
-        <v>-0.3776</v>
+        <v>-0.3734</v>
       </c>
       <c r="D118" t="n">
-        <v>-0.6105</v>
+        <v>-0.6284</v>
       </c>
       <c r="E118" t="n">
-        <v>-0.4683</v>
+        <v>-0.4631</v>
       </c>
       <c r="F118" t="n">
-        <v>-0.4683</v>
+        <v>-0.4631</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
       </c>
       <c r="H118" t="n">
-        <v>-0.4683</v>
+        <v>-0.4631</v>
       </c>
       <c r="I118" t="n">
         <v>-0.4749</v>
@@ -5878,25 +5878,25 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>-0.4817</v>
+        <v>-0.4764</v>
       </c>
       <c r="C119" t="n">
-        <v>-0.3884</v>
+        <v>-0.3841</v>
       </c>
       <c r="D119" t="n">
-        <v>-0.616</v>
+        <v>-0.6337</v>
       </c>
       <c r="E119" t="n">
-        <v>-0.4817</v>
+        <v>-0.4764</v>
       </c>
       <c r="F119" t="n">
-        <v>-0.4817</v>
+        <v>-0.4764</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
       </c>
       <c r="H119" t="n">
-        <v>-0.4817</v>
+        <v>-0.4764</v>
       </c>
       <c r="I119" t="n">
         <v>-0.4885</v>
@@ -5924,25 +5924,25 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>-0.5723</v>
+        <v>-0.5533</v>
       </c>
       <c r="C120" t="n">
-        <v>-0.4615</v>
+        <v>-0.4462</v>
       </c>
       <c r="D120" t="n">
-        <v>-0.6526</v>
+        <v>-0.6643</v>
       </c>
       <c r="E120" t="n">
-        <v>-0.5723</v>
+        <v>-0.5533</v>
       </c>
       <c r="F120" t="n">
-        <v>-0.5723</v>
+        <v>-0.5533</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
       </c>
       <c r="H120" t="n">
-        <v>-0.5723</v>
+        <v>-0.5533</v>
       </c>
       <c r="I120" t="n">
         <v>-0.5967</v>
@@ -5970,25 +5970,25 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>-0.6074000000000001</v>
+        <v>-0.594</v>
       </c>
       <c r="C121" t="n">
-        <v>-0.4898</v>
+        <v>-0.479</v>
       </c>
       <c r="D121" t="n">
-        <v>-0.6667</v>
+        <v>-0.6806</v>
       </c>
       <c r="E121" t="n">
-        <v>-0.6074000000000001</v>
+        <v>-0.594</v>
       </c>
       <c r="F121" t="n">
-        <v>-0.6074000000000001</v>
+        <v>-0.594</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
       </c>
       <c r="H121" t="n">
-        <v>-0.6074000000000001</v>
+        <v>-0.594</v>
       </c>
       <c r="I121" t="n">
         <v>-0.6246</v>
@@ -6016,25 +6016,25 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>-0.6776</v>
+        <v>-0.665</v>
       </c>
       <c r="C122" t="n">
-        <v>-0.5464</v>
+        <v>-0.5362</v>
       </c>
       <c r="D122" t="n">
-        <v>-0.6951000000000001</v>
+        <v>-0.7088</v>
       </c>
       <c r="E122" t="n">
-        <v>-0.6776</v>
+        <v>-0.665</v>
       </c>
       <c r="F122" t="n">
-        <v>-0.6776</v>
+        <v>-0.665</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
       </c>
       <c r="H122" t="n">
-        <v>-0.6776</v>
+        <v>-0.665</v>
       </c>
       <c r="I122" t="n">
         <v>-0.6935</v>
@@ -6062,25 +6062,25 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>-0.6915</v>
+        <v>-0.6813</v>
       </c>
       <c r="C123" t="n">
-        <v>-0.5576</v>
+        <v>-0.5494</v>
       </c>
       <c r="D123" t="n">
-        <v>-0.7007</v>
+        <v>-0.7153</v>
       </c>
       <c r="E123" t="n">
-        <v>-0.6915</v>
+        <v>-0.6813</v>
       </c>
       <c r="F123" t="n">
-        <v>-0.6915</v>
+        <v>-0.6813</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
       </c>
       <c r="H123" t="n">
-        <v>-0.6915</v>
+        <v>-0.6813</v>
       </c>
       <c r="I123" t="n">
         <v>-0.7045</v>
@@ -6108,25 +6108,25 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>-0.7004</v>
+        <v>-0.6875</v>
       </c>
       <c r="C124" t="n">
-        <v>-0.5648</v>
+        <v>-0.5544</v>
       </c>
       <c r="D124" t="n">
-        <v>-0.7043</v>
+        <v>-0.7178</v>
       </c>
       <c r="E124" t="n">
-        <v>-0.7004</v>
+        <v>-0.6875</v>
       </c>
       <c r="F124" t="n">
-        <v>-0.7004</v>
+        <v>-0.6875</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
       </c>
       <c r="H124" t="n">
-        <v>-0.7004</v>
+        <v>-0.6875</v>
       </c>
       <c r="I124" t="n">
         <v>-0.7169</v>
@@ -6150,93 +6150,93 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>wiz</t>
+          <t>CacaNito</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>-0.7121</v>
+        <v>-0.7093</v>
       </c>
       <c r="C125" t="n">
-        <v>-0.5742</v>
+        <v>-0.572</v>
       </c>
       <c r="D125" t="n">
-        <v>-0.709</v>
+        <v>-0.7265</v>
       </c>
       <c r="E125" t="n">
-        <v>-0.7121</v>
+        <v>-0.7093</v>
       </c>
       <c r="F125" t="n">
-        <v>-0.7121</v>
+        <v>-0.7093</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
       </c>
       <c r="H125" t="n">
-        <v>-0.7121</v>
+        <v>-0.7093</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.7154</v>
+        <v>-0.7213000000000001</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
       </c>
       <c r="K125" t="n">
-        <v>163</v>
+        <v>210</v>
       </c>
       <c r="L125" t="n">
         <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>-0.7154</v>
+        <v>-0.7213000000000001</v>
       </c>
       <c r="N125" t="n">
-        <v>163</v>
+        <v>210</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>CacaNito</t>
+          <t>wiz</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>-0.7146</v>
+        <v>-0.7094</v>
       </c>
       <c r="C126" t="n">
-        <v>-0.5762</v>
+        <v>-0.572</v>
       </c>
       <c r="D126" t="n">
-        <v>-0.71</v>
+        <v>-0.7265</v>
       </c>
       <c r="E126" t="n">
-        <v>-0.7146</v>
+        <v>-0.7094</v>
       </c>
       <c r="F126" t="n">
-        <v>-0.7146</v>
+        <v>-0.7094</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
       </c>
       <c r="H126" t="n">
-        <v>-0.7146</v>
+        <v>-0.7094</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.7213000000000001</v>
+        <v>-0.7154</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
       </c>
       <c r="K126" t="n">
-        <v>210</v>
+        <v>163</v>
       </c>
       <c r="L126" t="n">
         <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>-0.7213000000000001</v>
+        <v>-0.7154</v>
       </c>
       <c r="N126" t="n">
-        <v>210</v>
+        <v>163</v>
       </c>
     </row>
     <row r="127">
@@ -6246,25 +6246,25 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>-0.7532</v>
+        <v>-0.742</v>
       </c>
       <c r="C127" t="n">
-        <v>-0.6073</v>
+        <v>-0.5983000000000001</v>
       </c>
       <c r="D127" t="n">
-        <v>-0.7256</v>
+        <v>-0.7395</v>
       </c>
       <c r="E127" t="n">
-        <v>-0.7532</v>
+        <v>-0.742</v>
       </c>
       <c r="F127" t="n">
-        <v>-0.7532</v>
+        <v>-0.742</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
       </c>
       <c r="H127" t="n">
-        <v>-0.7532</v>
+        <v>-0.742</v>
       </c>
       <c r="I127" t="n">
         <v>-0.7673</v>
@@ -6288,185 +6288,185 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>nettik</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>-0.7844</v>
+        <v>-0.8038</v>
       </c>
       <c r="C128" t="n">
-        <v>-0.6325</v>
+        <v>-0.6482</v>
       </c>
       <c r="D128" t="n">
-        <v>-0.7382</v>
+        <v>-0.7641</v>
       </c>
       <c r="E128" t="n">
-        <v>-0.7844</v>
+        <v>-0.8038</v>
       </c>
       <c r="F128" t="n">
-        <v>2.2156</v>
+        <v>-0.8038</v>
       </c>
       <c r="G128" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="H128" t="n">
-        <v>2.2156</v>
+        <v>-0.8038</v>
       </c>
       <c r="I128" t="n">
-        <v>2.2782</v>
+        <v>-0.8106</v>
       </c>
       <c r="J128" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="K128" t="n">
-        <v>206</v>
+        <v>169</v>
       </c>
       <c r="L128" t="n">
-        <v>261</v>
+        <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>-0.7218</v>
+        <v>-0.8106</v>
       </c>
       <c r="N128" t="n">
-        <v>467</v>
+        <v>169</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>nettik</t>
+          <t>niko</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>-0.8068</v>
+        <v>-0.8332000000000001</v>
       </c>
       <c r="C129" t="n">
-        <v>-0.6506</v>
+        <v>-0.6719000000000001</v>
       </c>
       <c r="D129" t="n">
-        <v>-0.7473</v>
+        <v>-0.7759</v>
       </c>
       <c r="E129" t="n">
-        <v>-0.8068</v>
+        <v>-0.8332000000000001</v>
       </c>
       <c r="F129" t="n">
-        <v>-0.8068</v>
+        <v>-0.8332000000000001</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
       </c>
       <c r="H129" t="n">
-        <v>-0.8068</v>
+        <v>-0.8332000000000001</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.8106</v>
+        <v>-0.8544</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
       </c>
       <c r="K129" t="n">
-        <v>169</v>
+        <v>259</v>
       </c>
       <c r="L129" t="n">
         <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>-0.8106</v>
+        <v>-0.8544</v>
       </c>
       <c r="N129" t="n">
-        <v>169</v>
+        <v>259</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Snappi</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>-0.8414</v>
+        <v>-0.8335</v>
       </c>
       <c r="C130" t="n">
-        <v>-0.6785</v>
+        <v>-0.6721</v>
       </c>
       <c r="D130" t="n">
-        <v>-0.7613</v>
+        <v>-0.776</v>
       </c>
       <c r="E130" t="n">
-        <v>-0.8414</v>
+        <v>-0.8335</v>
       </c>
       <c r="F130" t="n">
-        <v>0.6795</v>
+        <v>2.1665</v>
       </c>
       <c r="G130" t="n">
-        <v>-1.5209</v>
+        <v>-3</v>
       </c>
       <c r="H130" t="n">
-        <v>0.6795</v>
+        <v>2.1665</v>
       </c>
       <c r="I130" t="n">
-        <v>0.6987</v>
+        <v>2.2782</v>
       </c>
       <c r="J130" t="n">
-        <v>-1.5209</v>
+        <v>-3</v>
       </c>
       <c r="K130" t="n">
-        <v>228</v>
+        <v>206</v>
       </c>
       <c r="L130" t="n">
-        <v>166</v>
+        <v>261</v>
       </c>
       <c r="M130" t="n">
-        <v>-0.8221999999999999</v>
+        <v>-0.7218</v>
       </c>
       <c r="N130" t="n">
-        <v>394</v>
+        <v>467</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>niko</t>
+          <t>Snappi</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>-0.8426</v>
+        <v>-0.8565</v>
       </c>
       <c r="C131" t="n">
-        <v>-0.6794</v>
+        <v>-0.6906</v>
       </c>
       <c r="D131" t="n">
-        <v>-0.7618</v>
+        <v>-0.7851</v>
       </c>
       <c r="E131" t="n">
-        <v>-0.8426</v>
+        <v>-0.8565</v>
       </c>
       <c r="F131" t="n">
-        <v>-0.8426</v>
+        <v>0.6644</v>
       </c>
       <c r="G131" t="n">
-        <v>0</v>
+        <v>-1.5209</v>
       </c>
       <c r="H131" t="n">
-        <v>-0.8426</v>
+        <v>0.6644</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.8544</v>
+        <v>0.6987</v>
       </c>
       <c r="J131" t="n">
-        <v>0</v>
+        <v>-1.5209</v>
       </c>
       <c r="K131" t="n">
-        <v>259</v>
+        <v>228</v>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="M131" t="n">
-        <v>-0.8544</v>
+        <v>-0.8221999999999999</v>
       </c>
       <c r="N131" t="n">
-        <v>259</v>
+        <v>394</v>
       </c>
     </row>
     <row r="132">
@@ -6476,25 +6476,25 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>-0.9557</v>
+        <v>-0.9241</v>
       </c>
       <c r="C132" t="n">
-        <v>-0.7706</v>
+        <v>-0.7452</v>
       </c>
       <c r="D132" t="n">
-        <v>-0.8074</v>
+        <v>-0.8121</v>
       </c>
       <c r="E132" t="n">
-        <v>-0.9557</v>
+        <v>-0.9241</v>
       </c>
       <c r="F132" t="n">
-        <v>-0.9557</v>
+        <v>-0.9241</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
       </c>
       <c r="H132" t="n">
-        <v>-0.9557</v>
+        <v>-0.9241</v>
       </c>
       <c r="I132" t="n">
         <v>-0.9965000000000001</v>
@@ -6522,25 +6522,25 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>-1.018</v>
+        <v>-0.9955000000000001</v>
       </c>
       <c r="C133" t="n">
-        <v>-0.8209</v>
+        <v>-0.8027</v>
       </c>
       <c r="D133" t="n">
-        <v>-0.8326</v>
+        <v>-0.8405</v>
       </c>
       <c r="E133" t="n">
-        <v>-1.018</v>
+        <v>-0.9955000000000001</v>
       </c>
       <c r="F133" t="n">
-        <v>-1.018</v>
+        <v>-0.9955000000000001</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
       </c>
       <c r="H133" t="n">
-        <v>-1.018</v>
+        <v>-0.9955000000000001</v>
       </c>
       <c r="I133" t="n">
         <v>-1.0468</v>
@@ -6568,25 +6568,25 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>-1.0808</v>
+        <v>-1.0529</v>
       </c>
       <c r="C134" t="n">
-        <v>-0.8715000000000001</v>
+        <v>-0.849</v>
       </c>
       <c r="D134" t="n">
-        <v>-0.858</v>
+        <v>-0.8633999999999999</v>
       </c>
       <c r="E134" t="n">
-        <v>-1.0808</v>
+        <v>-1.0529</v>
       </c>
       <c r="F134" t="n">
-        <v>-1.0808</v>
+        <v>-1.0529</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
       </c>
       <c r="H134" t="n">
-        <v>-1.0808</v>
+        <v>-1.0529</v>
       </c>
       <c r="I134" t="n">
         <v>-1.1165</v>
@@ -6614,25 +6614,25 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>-1.1902</v>
+        <v>-1.1857</v>
       </c>
       <c r="C135" t="n">
-        <v>-0.9597</v>
+        <v>-0.9560999999999999</v>
       </c>
       <c r="D135" t="n">
-        <v>-0.9022</v>
+        <v>-0.9163</v>
       </c>
       <c r="E135" t="n">
-        <v>-1.1902</v>
+        <v>-1.1857</v>
       </c>
       <c r="F135" t="n">
-        <v>-1.1902</v>
+        <v>-1.1857</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
       </c>
       <c r="H135" t="n">
-        <v>-1.1902</v>
+        <v>-1.1857</v>
       </c>
       <c r="I135" t="n">
         <v>-1.1957</v>
@@ -6660,25 +6660,25 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>-1.223</v>
+        <v>-1.1959</v>
       </c>
       <c r="C136" t="n">
-        <v>-0.9862</v>
+        <v>-0.9643</v>
       </c>
       <c r="D136" t="n">
-        <v>-0.9154</v>
+        <v>-0.9204</v>
       </c>
       <c r="E136" t="n">
-        <v>-1.223</v>
+        <v>-1.1959</v>
       </c>
       <c r="F136" t="n">
-        <v>-1.223</v>
+        <v>-1.1959</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
       </c>
       <c r="H136" t="n">
-        <v>-1.223</v>
+        <v>-1.1959</v>
       </c>
       <c r="I136" t="n">
         <v>-1.2576</v>
@@ -6706,25 +6706,25 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>-1.2894</v>
+        <v>-1.2798</v>
       </c>
       <c r="C137" t="n">
-        <v>-1.0397</v>
+        <v>-1.032</v>
       </c>
       <c r="D137" t="n">
-        <v>-0.9423</v>
+        <v>-0.9538</v>
       </c>
       <c r="E137" t="n">
-        <v>-1.2894</v>
+        <v>-1.2798</v>
       </c>
       <c r="F137" t="n">
-        <v>-1.2894</v>
+        <v>-1.2798</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
       </c>
       <c r="H137" t="n">
-        <v>-1.2894</v>
+        <v>-1.2798</v>
       </c>
       <c r="I137" t="n">
         <v>-1.3014</v>
@@ -6752,25 +6752,25 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>-1.4338</v>
+        <v>-1.4285</v>
       </c>
       <c r="C138" t="n">
-        <v>-1.1562</v>
+        <v>-1.1519</v>
       </c>
       <c r="D138" t="n">
-        <v>-1.0006</v>
+        <v>-1.013</v>
       </c>
       <c r="E138" t="n">
-        <v>-1.4338</v>
+        <v>-1.4285</v>
       </c>
       <c r="F138" t="n">
-        <v>-1.4338</v>
+        <v>-1.4285</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
       </c>
       <c r="H138" t="n">
-        <v>-1.4338</v>
+        <v>-1.4285</v>
       </c>
       <c r="I138" t="n">
         <v>-1.4405</v>
@@ -6798,25 +6798,25 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>-1.489</v>
+        <v>-1.4724</v>
       </c>
       <c r="C139" t="n">
-        <v>-1.2007</v>
+        <v>-1.1873</v>
       </c>
       <c r="D139" t="n">
-        <v>-1.0229</v>
+        <v>-1.0305</v>
       </c>
       <c r="E139" t="n">
-        <v>-1.489</v>
+        <v>-1.4724</v>
       </c>
       <c r="F139" t="n">
-        <v>-1.489</v>
+        <v>-1.4724</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
       </c>
       <c r="H139" t="n">
-        <v>-1.489</v>
+        <v>-1.4724</v>
       </c>
       <c r="I139" t="n">
         <v>-1.5099</v>
@@ -6844,25 +6844,25 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>-1.5373</v>
+        <v>-1.5032</v>
       </c>
       <c r="C140" t="n">
-        <v>-1.2396</v>
+        <v>-1.2121</v>
       </c>
       <c r="D140" t="n">
-        <v>-1.0424</v>
+        <v>-1.0428</v>
       </c>
       <c r="E140" t="n">
-        <v>-1.5373</v>
+        <v>-1.5032</v>
       </c>
       <c r="F140" t="n">
-        <v>-1.5373</v>
+        <v>-1.5032</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
       </c>
       <c r="H140" t="n">
-        <v>-1.5373</v>
+        <v>-1.5032</v>
       </c>
       <c r="I140" t="n">
         <v>-1.5807</v>
@@ -6890,25 +6890,25 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>-1.5571</v>
+        <v>-1.5455</v>
       </c>
       <c r="C141" t="n">
-        <v>-1.2556</v>
+        <v>-1.2462</v>
       </c>
       <c r="D141" t="n">
-        <v>-1.0504</v>
+        <v>-1.0596</v>
       </c>
       <c r="E141" t="n">
-        <v>-1.5571</v>
+        <v>-1.5455</v>
       </c>
       <c r="F141" t="n">
-        <v>-1.5571</v>
+        <v>-1.5455</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
       </c>
       <c r="H141" t="n">
-        <v>-1.5571</v>
+        <v>-1.5455</v>
       </c>
       <c r="I141" t="n">
         <v>-1.5716</v>
@@ -6936,25 +6936,25 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>-1.6623</v>
+        <v>-1.6499</v>
       </c>
       <c r="C142" t="n">
-        <v>-1.3404</v>
+        <v>-1.3304</v>
       </c>
       <c r="D142" t="n">
-        <v>-1.0929</v>
+        <v>-1.1012</v>
       </c>
       <c r="E142" t="n">
-        <v>-1.6623</v>
+        <v>-1.6499</v>
       </c>
       <c r="F142" t="n">
-        <v>-1.6623</v>
+        <v>-1.6499</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
       </c>
       <c r="H142" t="n">
-        <v>-1.6623</v>
+        <v>-1.6499</v>
       </c>
       <c r="I142" t="n">
         <v>-1.6778</v>
@@ -6982,25 +6982,25 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>-1.7012</v>
+        <v>-1.6511</v>
       </c>
       <c r="C143" t="n">
-        <v>-1.3718</v>
+        <v>-1.3314</v>
       </c>
       <c r="D143" t="n">
-        <v>-1.1086</v>
+        <v>-1.1017</v>
       </c>
       <c r="E143" t="n">
-        <v>-1.7012</v>
+        <v>-1.6511</v>
       </c>
       <c r="F143" t="n">
-        <v>-1.7012</v>
+        <v>-1.6511</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
       </c>
       <c r="H143" t="n">
-        <v>-1.7012</v>
+        <v>-1.6511</v>
       </c>
       <c r="I143" t="n">
         <v>-1.7656</v>
@@ -7028,25 +7028,25 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>-1.707</v>
+        <v>-1.6943</v>
       </c>
       <c r="C144" t="n">
-        <v>-1.3765</v>
+        <v>-1.3662</v>
       </c>
       <c r="D144" t="n">
-        <v>-1.111</v>
+        <v>-1.1189</v>
       </c>
       <c r="E144" t="n">
-        <v>-1.707</v>
+        <v>-1.6943</v>
       </c>
       <c r="F144" t="n">
-        <v>-1.707</v>
+        <v>-1.6943</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
       </c>
       <c r="H144" t="n">
-        <v>-1.707</v>
+        <v>-1.6943</v>
       </c>
       <c r="I144" t="n">
         <v>-1.7229</v>
@@ -7074,25 +7074,25 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>-1.7333</v>
+        <v>-1.7076</v>
       </c>
       <c r="C145" t="n">
-        <v>-1.3977</v>
+        <v>-1.3769</v>
       </c>
       <c r="D145" t="n">
-        <v>-1.1216</v>
+        <v>-1.1242</v>
       </c>
       <c r="E145" t="n">
-        <v>-1.7333</v>
+        <v>-1.7076</v>
       </c>
       <c r="F145" t="n">
-        <v>-1.7333</v>
+        <v>-1.7076</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
       </c>
       <c r="H145" t="n">
-        <v>-1.7333</v>
+        <v>-1.7076</v>
       </c>
       <c r="I145" t="n">
         <v>-1.7658</v>
@@ -7120,25 +7120,25 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>-1.9122</v>
+        <v>-1.8559</v>
       </c>
       <c r="C146" t="n">
-        <v>-1.5419</v>
+        <v>-1.4965</v>
       </c>
       <c r="D146" t="n">
-        <v>-1.1938</v>
+        <v>-1.1833</v>
       </c>
       <c r="E146" t="n">
-        <v>-1.9122</v>
+        <v>-1.8559</v>
       </c>
       <c r="F146" t="n">
-        <v>-1.9122</v>
+        <v>-1.8559</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
       </c>
       <c r="H146" t="n">
-        <v>-1.9122</v>
+        <v>-1.8559</v>
       </c>
       <c r="I146" t="n">
         <v>-1.9846</v>
@@ -7166,25 +7166,25 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>-1.9423</v>
+        <v>-1.9206</v>
       </c>
       <c r="C147" t="n">
-        <v>-1.5662</v>
+        <v>-1.5487</v>
       </c>
       <c r="D147" t="n">
-        <v>-1.206</v>
+        <v>-1.2091</v>
       </c>
       <c r="E147" t="n">
-        <v>-1.9423</v>
+        <v>-1.9206</v>
       </c>
       <c r="F147" t="n">
-        <v>-1.9423</v>
+        <v>-1.9206</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
       </c>
       <c r="H147" t="n">
-        <v>-1.9423</v>
+        <v>-1.9206</v>
       </c>
       <c r="I147" t="n">
         <v>-1.9695</v>
@@ -7212,25 +7212,25 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>-2.0673</v>
+        <v>-2.0139</v>
       </c>
       <c r="C148" t="n">
-        <v>-1.667</v>
+        <v>-1.6239</v>
       </c>
       <c r="D148" t="n">
-        <v>-1.2565</v>
+        <v>-1.2462</v>
       </c>
       <c r="E148" t="n">
-        <v>-2.0673</v>
+        <v>-2.0139</v>
       </c>
       <c r="F148" t="n">
-        <v>-2.0673</v>
+        <v>-2.0139</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
       </c>
       <c r="H148" t="n">
-        <v>-2.0673</v>
+        <v>-2.0139</v>
       </c>
       <c r="I148" t="n">
         <v>-2.1356</v>
@@ -7258,25 +7258,25 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>-2.1873</v>
+        <v>-2.1388</v>
       </c>
       <c r="C149" t="n">
-        <v>-1.7638</v>
+        <v>-1.7246</v>
       </c>
       <c r="D149" t="n">
-        <v>-1.305</v>
+        <v>-1.296</v>
       </c>
       <c r="E149" t="n">
-        <v>-2.1873</v>
+        <v>-2.1388</v>
       </c>
       <c r="F149" t="n">
-        <v>-2.1873</v>
+        <v>-2.1388</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
       </c>
       <c r="H149" t="n">
-        <v>-2.1873</v>
+        <v>-2.1388</v>
       </c>
       <c r="I149" t="n">
         <v>-2.2491</v>
@@ -7304,25 +7304,25 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>-2.2237</v>
+        <v>-2.2155</v>
       </c>
       <c r="C150" t="n">
-        <v>-1.7931</v>
+        <v>-1.7865</v>
       </c>
       <c r="D150" t="n">
-        <v>-1.3197</v>
+        <v>-1.3266</v>
       </c>
       <c r="E150" t="n">
-        <v>-2.2237</v>
+        <v>-2.2155</v>
       </c>
       <c r="F150" t="n">
-        <v>-2.2237</v>
+        <v>-2.2155</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
       </c>
       <c r="H150" t="n">
-        <v>-2.2237</v>
+        <v>-2.2155</v>
       </c>
       <c r="I150" t="n">
         <v>-2.2341</v>
@@ -7350,25 +7350,25 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>-2.2804</v>
+        <v>-2.255</v>
       </c>
       <c r="C151" t="n">
-        <v>-1.8388</v>
+        <v>-1.8183</v>
       </c>
       <c r="D151" t="n">
-        <v>-1.3426</v>
+        <v>-1.3423</v>
       </c>
       <c r="E151" t="n">
-        <v>-2.2804</v>
+        <v>-2.255</v>
       </c>
       <c r="F151" t="n">
-        <v>-2.2804</v>
+        <v>-2.255</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
       </c>
       <c r="H151" t="n">
-        <v>-2.2804</v>
+        <v>-2.255</v>
       </c>
       <c r="I151" t="n">
         <v>-2.3124</v>
@@ -7396,25 +7396,25 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>-2.4541</v>
+        <v>-2.4358</v>
       </c>
       <c r="C152" t="n">
-        <v>-1.9789</v>
+        <v>-1.9641</v>
       </c>
       <c r="D152" t="n">
-        <v>-1.4128</v>
+        <v>-1.4143</v>
       </c>
       <c r="E152" t="n">
-        <v>-2.4541</v>
+        <v>-2.4358</v>
       </c>
       <c r="F152" t="n">
-        <v>-2.4541</v>
+        <v>-2.4358</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
       </c>
       <c r="H152" t="n">
-        <v>-2.4541</v>
+        <v>-2.4358</v>
       </c>
       <c r="I152" t="n">
         <v>-2.477</v>
@@ -7442,25 +7442,25 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>-2.5029</v>
+        <v>-2.4935</v>
       </c>
       <c r="C153" t="n">
-        <v>-2.0182</v>
+        <v>-2.0107</v>
       </c>
       <c r="D153" t="n">
-        <v>-1.4325</v>
+        <v>-1.4373</v>
       </c>
       <c r="E153" t="n">
-        <v>-2.5029</v>
+        <v>-2.4935</v>
       </c>
       <c r="F153" t="n">
-        <v>-2.5029</v>
+        <v>-2.4935</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
       </c>
       <c r="H153" t="n">
-        <v>-2.5029</v>
+        <v>-2.4935</v>
       </c>
       <c r="I153" t="n">
         <v>-2.5145</v>
@@ -7484,185 +7484,185 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>djay</t>
+          <t>drop</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>-2.583</v>
+        <v>-2.5073</v>
       </c>
       <c r="C154" t="n">
-        <v>-2.0828</v>
+        <v>-2.0218</v>
       </c>
       <c r="D154" t="n">
-        <v>-1.4648</v>
+        <v>-1.4428</v>
       </c>
       <c r="E154" t="n">
-        <v>-2.583</v>
+        <v>-2.5073</v>
       </c>
       <c r="F154" t="n">
-        <v>-2.583</v>
+        <v>-2.5073</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
       </c>
       <c r="H154" t="n">
-        <v>-2.583</v>
+        <v>-2.5073</v>
       </c>
       <c r="I154" t="n">
-        <v>-2.6071</v>
+        <v>-2.6812</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
       </c>
       <c r="K154" t="n">
-        <v>210</v>
+        <v>400</v>
       </c>
       <c r="L154" t="n">
         <v>0</v>
       </c>
       <c r="M154" t="n">
-        <v>-2.6071</v>
+        <v>-2.6812</v>
       </c>
       <c r="N154" t="n">
-        <v>210</v>
+        <v>400</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>drop</t>
+          <t>MAJ3R</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>-2.5834</v>
+        <v>-2.5352</v>
       </c>
       <c r="C155" t="n">
-        <v>-2.0831</v>
+        <v>-2.0443</v>
       </c>
       <c r="D155" t="n">
-        <v>-1.465</v>
+        <v>-1.4539</v>
       </c>
       <c r="E155" t="n">
-        <v>-2.5834</v>
+        <v>-2.5352</v>
       </c>
       <c r="F155" t="n">
-        <v>-2.5834</v>
+        <v>-2.5352</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
       </c>
       <c r="H155" t="n">
-        <v>-2.5834</v>
+        <v>-2.5352</v>
       </c>
       <c r="I155" t="n">
-        <v>-2.6812</v>
+        <v>-2.666</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
       </c>
       <c r="K155" t="n">
-        <v>400</v>
+        <v>329</v>
       </c>
       <c r="L155" t="n">
         <v>0</v>
       </c>
       <c r="M155" t="n">
-        <v>-2.6812</v>
+        <v>-2.666</v>
       </c>
       <c r="N155" t="n">
-        <v>400</v>
+        <v>329</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>MAJ3R</t>
+          <t>NEKIZ</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>-2.5927</v>
+        <v>-2.5421</v>
       </c>
       <c r="C156" t="n">
-        <v>-2.0906</v>
+        <v>-2.0498</v>
       </c>
       <c r="D156" t="n">
-        <v>-1.4688</v>
+        <v>-1.4567</v>
       </c>
       <c r="E156" t="n">
-        <v>-2.5927</v>
+        <v>-2.5421</v>
       </c>
       <c r="F156" t="n">
-        <v>-2.5927</v>
+        <v>-2.5421</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
       </c>
       <c r="H156" t="n">
-        <v>-2.5927</v>
+        <v>-2.5421</v>
       </c>
       <c r="I156" t="n">
-        <v>-2.666</v>
+        <v>-2.7413</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
       </c>
       <c r="K156" t="n">
-        <v>329</v>
+        <v>396</v>
       </c>
       <c r="L156" t="n">
         <v>0</v>
       </c>
       <c r="M156" t="n">
-        <v>-2.666</v>
+        <v>-2.7413</v>
       </c>
       <c r="N156" t="n">
-        <v>329</v>
+        <v>396</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>NEKIZ</t>
+          <t>djay</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>-2.6291</v>
+        <v>-2.5638</v>
       </c>
       <c r="C157" t="n">
-        <v>-2.12</v>
+        <v>-2.0673</v>
       </c>
       <c r="D157" t="n">
-        <v>-1.4835</v>
+        <v>-1.4653</v>
       </c>
       <c r="E157" t="n">
-        <v>-2.6291</v>
+        <v>-2.5638</v>
       </c>
       <c r="F157" t="n">
-        <v>-2.6291</v>
+        <v>-2.5638</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
       </c>
       <c r="H157" t="n">
-        <v>-2.6291</v>
+        <v>-2.5638</v>
       </c>
       <c r="I157" t="n">
-        <v>-2.7413</v>
+        <v>-2.6071</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
       </c>
       <c r="K157" t="n">
-        <v>396</v>
+        <v>210</v>
       </c>
       <c r="L157" t="n">
         <v>0</v>
       </c>
       <c r="M157" t="n">
-        <v>-2.7413</v>
+        <v>-2.6071</v>
       </c>
       <c r="N157" t="n">
-        <v>396</v>
+        <v>210</v>
       </c>
     </row>
     <row r="158">
@@ -7672,25 +7672,25 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>-2.7327</v>
+        <v>-2.6721</v>
       </c>
       <c r="C158" t="n">
-        <v>-2.2035</v>
+        <v>-2.1547</v>
       </c>
       <c r="D158" t="n">
-        <v>-1.5253</v>
+        <v>-1.5085</v>
       </c>
       <c r="E158" t="n">
-        <v>-2.7327</v>
+        <v>-2.6721</v>
       </c>
       <c r="F158" t="n">
-        <v>-2.7327</v>
+        <v>-2.6721</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
       </c>
       <c r="H158" t="n">
-        <v>-2.7327</v>
+        <v>-2.6721</v>
       </c>
       <c r="I158" t="n">
         <v>-2.8099</v>
@@ -7718,25 +7718,25 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>-2.778</v>
+        <v>-2.6794</v>
       </c>
       <c r="C159" t="n">
-        <v>-2.2401</v>
+        <v>-2.1606</v>
       </c>
       <c r="D159" t="n">
-        <v>-1.5436</v>
+        <v>-1.5114</v>
       </c>
       <c r="E159" t="n">
-        <v>-2.778</v>
+        <v>-2.6794</v>
       </c>
       <c r="F159" t="n">
-        <v>-2.4494</v>
+        <v>-2.3508</v>
       </c>
       <c r="G159" t="n">
         <v>-0.3286</v>
       </c>
       <c r="H159" t="n">
-        <v>-2.4494</v>
+        <v>-2.3508</v>
       </c>
       <c r="I159" t="n">
         <v>-2.5778</v>
@@ -7764,25 +7764,25 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>-3.1244</v>
+        <v>-3.0666</v>
       </c>
       <c r="C160" t="n">
-        <v>-2.5194</v>
+        <v>-2.4728</v>
       </c>
       <c r="D160" t="n">
-        <v>-1.6836</v>
+        <v>-1.6656</v>
       </c>
       <c r="E160" t="n">
-        <v>-3.1244</v>
+        <v>-3.0666</v>
       </c>
       <c r="F160" t="n">
-        <v>-3.1244</v>
+        <v>-3.0666</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
       </c>
       <c r="H160" t="n">
-        <v>-3.1244</v>
+        <v>-3.0666</v>
       </c>
       <c r="I160" t="n">
         <v>-3.1978</v>
@@ -7810,25 +7810,25 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>-3.8555</v>
+        <v>-3.7279</v>
       </c>
       <c r="C161" t="n">
-        <v>-3.1089</v>
+        <v>-3.006</v>
       </c>
       <c r="D161" t="n">
-        <v>-1.9789</v>
+        <v>-1.9291</v>
       </c>
       <c r="E161" t="n">
-        <v>-3.8555</v>
+        <v>-3.7279</v>
       </c>
       <c r="F161" t="n">
-        <v>-3.8555</v>
+        <v>-3.7279</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
       </c>
       <c r="H161" t="n">
-        <v>-3.8555</v>
+        <v>-3.7279</v>
       </c>
       <c r="I161" t="n">
         <v>-4.02</v>
@@ -7856,25 +7856,25 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>-4.7922</v>
+        <v>-4.6511</v>
       </c>
       <c r="C162" t="n">
-        <v>-3.8642</v>
+        <v>-3.7505</v>
       </c>
       <c r="D162" t="n">
-        <v>-2.3573</v>
+        <v>-2.2969</v>
       </c>
       <c r="E162" t="n">
-        <v>-4.7922</v>
+        <v>-4.6511</v>
       </c>
       <c r="F162" t="n">
-        <v>-4.7922</v>
+        <v>-4.6511</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
       </c>
       <c r="H162" t="n">
-        <v>-4.7922</v>
+        <v>-4.6511</v>
       </c>
       <c r="I162" t="n">
         <v>-4.9736</v>
